--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -1854,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1958,17 +1958,17 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>日本語シャワー</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>朝のニュース</t>
+          <t>ニュース</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>桜が満開</t>
+          <t>桜が満開（国内）</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2028,60 +2028,60 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>日本語シャワー</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ラジオ風トーク</t>
+          <t>ニュース</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>続かない人へ</t>
+          <t>全国の天気（天気）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>トーク</t>
+          <t>天気予報</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
+          <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Good evening, this is your host, Yuki. Thanks for your hard work today. Now, a message from a listener: 'Lately I can't keep up my Japanese study and I'm troubled.' I understand! But it's okay. Even 5 minutes a day is fine. Keep it up enjoyably with dramas or songs you like. Now, tonight's song.</t>
+          <t>Here's the nationwide weather. Today it's sunny in western Japan, but in eastern Japan clouds will increase from the afternoon. Some areas may see rain at night. It's safer to take an umbrella. Temperatures will be around 20 degrees—a comfortable day.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>お疲れさまでした／お便り／〜ましょう</t>
+          <t>晴れます／雲が 多く なる／傘を 持って</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>ラジオの語り口・呼びかけ。</t>
+          <t>全国天気の聞き取り（地域差）。</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>親近感で“夜の習慣”に。</t>
+          <t>「傘いる?」毎朝役立つ。</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1話者・パーソナリティ調</t>
+          <t>1話者・予報士調</t>
         </is>
       </c>
     </row>
@@ -2098,60 +2098,60 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>日本語シャワー</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>今日の天気</t>
+          <t>ニュース</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>全国の天気</t>
+          <t>海外のニュース（国際）</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>天気予報</t>
+          <t>ニュース</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
+          <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Here's the nationwide weather. Today it's sunny in western Japan, but in eastern Japan clouds will increase from the afternoon. Some areas may see rain at night. It's safer to take an umbrella. Temperatures will be around 20 degrees—a comfortable day.</t>
+          <t>Hello, international news. In the U.S., a conference on new technology was held. Many researchers gathered from around the world. Many companies from Japan also took part and are drawing attention. Next year, the same conference is scheduled to be held in Asia too.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>晴れます／雲が 多く なる／傘を 持って</t>
+          <t>国際ニュース／〜が 開かれました／注目を 集めています</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>全国天気の聞き取り（地域差）。</t>
+          <t>国際ニュースの定型表現。</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>「傘いる?」毎朝役立つ。</t>
+          <t>世界とつながる話題。</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1話者・予報士調</t>
+          <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>
@@ -2168,22 +2168,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>カイの日記</t>
+          <t>ニュース</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>はじめての美容院</t>
+          <t>サッカーの試合（スポーツ）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>ニュース</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2193,35 +2193,35 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>今日（きょう）は はじめて 一人（ひとり）で 美容院（びよういん）に 行（い）った。日本語（にほんご）で 髪型（かみがた）を 説明（せつめい）するのは ドキドキした。「少（すこ）し 短（みじか）く してください」と 言（い）ったら、思（おも）ったより ずいぶん 短く なって しまった。でも、美容師（びようし）さんが 「似合（にあ）っていますよ」と 言ってくれたので、うれしかった。次（つぎ）は もっと くわしく 伝（つた）えられるように なりたい。</t>
+          <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Today I went to a hair salon alone for the first time. Explaining my hairstyle in Japanese was nerve-racking. When I said 'a little shorter, please,' it came out much shorter than I expected. But the stylist said 'It suits you,' so I was happy. Next time I want to explain in more detail.</t>
+          <t>Sports news. Yesterday there was a soccer match. The Japan team won 2 to 1. The final goal was wonderful. Fans in the stadium cheered loudly. The next match is next Saturday. Something to look forward to.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>はじめて 一人で／〜てしまった／似合っています</t>
+          <t>2対1で 勝ちました／応援しました／楽しみですね</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>体験＋気持ちの流れを読む。</t>
+          <t>スポーツ結果(点数/勝敗)の聞き取り。</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>カイの小さな成長＝連載で愛着。</t>
+          <t>勝利の興奮。</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>
@@ -2238,22 +2238,22 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>こわい話</t>
+          <t>お便り相談室</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>真夜中の水の音</t>
+          <t>勉強が続かない</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>トーク</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -2263,35 +2263,35 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>夜中（よなか）、トイレに 起（お）きた。家（いえ）には 私（わたし）一人（ひとり）の はずだった。でも、台所（だいどころ）から 水（みず）の 音（おと）が 聞（き）こえる。だれかが 蛇口（じゃぐち）を 使（つか）っている…？こわごわ のぞくと、誰（だれ）も いない。ただ、コップに 水が いっぱい 入（はい）っていた。私（わたし）は 飲（の）んでいない。あの 水は、だれが…。</t>
+          <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>In the middle of the night, I got up for the toilet. I should have been alone in the house. But I heard the sound of water from the kitchen. Was someone using the faucet...? Fearfully I peeked in—no one. Just a glass full of water. I hadn't poured it. Who filled that glass...?</t>
+          <t>Good evening, this is your host, Yuki. Thanks for your hard work today. Now, a message from a listener: 'Lately I can't keep up my Japanese study and I'm troubled.' I understand! But it's okay. Even 5 minutes a day is fine. Keep it up enjoyably with dramas or songs you like. Now, tonight's song.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>〜のはず／聞こえる／だれも いない</t>
+          <t>お疲れさまでした／お便り／〜ましょう</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>怪談の“間”と落ちを味わう。</t>
+          <t>相談＋励ましの語り口。</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>ゾクッとする中毒性。</t>
+          <t>共感＝続けたくなる。</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1話者・低めの声</t>
+          <t>1話者・パーソナリティ調</t>
         </is>
       </c>
     </row>
@@ -2308,60 +2308,60 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>昔話</t>
+          <t>お便り相談室</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>桃太郎</t>
+          <t>漢字が覚えられない</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>トーク</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が 流（なが）れて きました。おばあさんが 桃を 切（き）ると、中（なか）から 元気（げんき）な 男（おとこ）の子（こ）が 生（う）まれました。名前（なまえ）を 桃太郎（ももたろう）と つけました。桃太郎は 大（おお）きく なって、鬼（おに）を 退治（たいじ）しに 行くことに しました。</t>
+          <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Long ago, in a certain place, lived an old man and an old woman. One day, a big peach came floating down the river. When the old woman cut it open, a healthy boy was born from inside. They named him Momotaro. Momotaro grew up and decided to go defeat the ogres.</t>
+          <t>Today's listener message: 'I just can't memorize kanji.' I understand—there are so many. My tip: learn a little every day, from kanji you see in daily life. Signs and menus make good study material too. Don't rush—keep at it.</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>むかしむかし／〜と いいました／〜ことに した</t>
+          <t>なかなか 〜られません／少しずつ／あせらず 続けましょう</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>昔話の定型表現に親しむ。</t>
+          <t>相談＋アドバイスの語り。</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>有名な物語で親しみやすい。</t>
+          <t>共感＆励ましで続く。</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1話者・語り</t>
+          <t>1話者・パーソナリティ調</t>
         </is>
       </c>
     </row>
@@ -2378,60 +2378,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>本音講座</t>
+          <t>ゲストインタビュー</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>「大丈夫です」の正体</t>
+          <t>ベトナムから来たグエンさん</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>解説</t>
+          <t>対話</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
+          <t>司会（しかい）：今日（きょう）の ゲストは、ベトナムから 来（き）た グエンさんです。日本（にほん）に 来て どのくらいですか。
+グエン：2年（ねん）です。
+司会：日本で 一番（いちばん）好（す）きな ものは？
+グエン：温泉（おんせん）です。とても 気持（きも）ちが いいです。
+司会：これから 何（なに）を したいですか。
+グエン：日本語（にほんご）を もっと 上手（じょうず）に なりたいです。
+司会：いいですね！ がんばってください。</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
+          <t>Host: Today's guest is Guen from Vietnam. How long have you been in Japan? / Guen: Two years. / Host: What's your favorite thing in Japan? / Guen: Hot springs. They feel so good. / Host: What do you want to do from now on? / Guen: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
+          <t>どのくらいですか／一番 好きな ものは？／がんばってください</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>多義的な「大丈夫」を読み解く。</t>
+          <t>インタビューの定番質問。</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>「え、両方!?」の発見＝SNS映え。</t>
+          <t>多様な人の声・人間味。</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1話者・解説</t>
+          <t>多声TTS:司会/ゲスト</t>
         </is>
       </c>
     </row>
@@ -2448,22 +2454,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
+          <t>ラジオトーク</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>あるある</t>
+          <t>2人のフリートーク</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>日本の電車は静か</t>
+          <t>週末どうだった？</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>読み物</t>
+          <t>対話</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2473,35 +2479,40 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
+          <t>A：週末（しゅうまつ）、どうだった？
+B：友（とも）だちと 海（うみ）に 行（い）ったよ。すごく きれいだった！
+A：いいなあ。私（わたし）は 一日中（いちにちじゅう）、家（いえ）で ドラマを 見（み）てた。
+B：それも いいよね。何（なに）の ドラマ？
+A：日本（にほん）の 恋愛（れんあい）ドラマ。じつは 日本語の 勉強（べんきょう）にも なるんだ。
+B：へえ、いいね！</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
+          <t>A: How was your weekend? / B: I went to the beach with friends. It was so beautiful! / A: Nice. I watched dramas at home all day. / B: That's good too. What drama? / A: A Japanese romance drama. Actually it's good Japanese study too. / B: Oh, nice!</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>〜と、〜／ほとんど 話しません／心地よい</t>
+          <t>どうだった?／〜に 行ったよ／勉強にも なる</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>文化比較の読み物。</t>
+          <t>友だち同士の自然な雑談。</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>「わかる!」共感で拡散。</t>
+          <t>ゆるい会話＝多聴に最適。</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
+          <t>多声TTS:友人2人</t>
         </is>
       </c>
     </row>
@@ -2518,58 +2529,688 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>カイのストーリー</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>空港に着いた</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>一人称</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）に 着（つ）いた。空港（くうこう）は とても 大（おお）きい。入国（にゅうこく）の 列（れつ）は 長（なが）かったけれど、係（かか）りの 人（ひと）は やさしかった。「ようこそ」と 言（い）ってくれた。荷物（にもつ）を 受（う）け取（と）って、電車（でんしゃ）の 駅（えき）を さがす。さあ、新（あたら）しい 生活（せいかつ）の はじまりだ。</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>I arrived in Japan. The airport is huge. The immigration line was long, but the staff were kind. They said 'Welcome.' I picked up my luggage and looked for the train station. Now, my new life begins.</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>〜に 着いた／〜けれど／はじまりだ</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>到着〜移動の体験＋気持ち。</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>新生活スタート（カイ連載 第1話）。</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>1話者・カイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>L-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>カイのストーリー</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>はじめての一人暮らし</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>一人称</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>今日（きょう）から 一人暮（ひとりぐ）らしだ。部屋（へや）は 小（ちい）さいけれど、自分（じぶん）だけの 場所（ばしょ）だ。でも、困（こま）ったことが ある。ゴミの 出（だ）し方（かた）が わからない。となりの 人（ひと）に 聞（き）いたら、ていねいに 教（おし）えてくれた。日本（にほん）の 人は 親切（しんせつ）だなと 思（おも）った。</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>From today I live alone. The room is small, but it's my own place. But there's a problem—I don't know how to sort the trash. When I asked my neighbor, they kindly explained. I thought, Japanese people are so kind.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>一人暮らし／〜けれど／教えてくれた</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>生活立ち上げの戸惑いと人の温かさ。</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>短文「生活力」と再会＝らせん。</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>1話者・カイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>L-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>カイのストーリー</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>京都へ行く</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>一人称</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>連休（れんきゅう）に、はじめて 京都（きょうと）へ 行（い）った。古（ふる）い お寺（てら）が たくさん あって、とても 美（うつく）しかった。着物（きもの）を 着（き）て 歩（ある）いている 人も いた。お昼（ひる）に 食（た）べた 抹茶（まっちゃ）の アイスは、わすれられない 味（あじ）だった。また 行きたい。</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>On the holidays, I went to Kyoto for the first time. There were many old temples, and they were very beautiful. Some people walked around in kimono. The matcha ice cream I had for lunch was an unforgettable taste. I want to go again.</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>はじめて 〜へ 行った／〜も いた／また 行きたい</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>旅行の描写＋感想。</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>旅情・食・文化。</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>1話者・カイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>L-012</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>カイのストーリー</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>はじめての美容院</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>一人称</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>今日（きょう）は はじめて 一人（ひとり）で 美容院（びよういん）に 行（い）った。日本語（にほんご）で 髪型（かみがた）を 説明（せつめい）するのは ドキドキした。「少（すこ）し 短（みじか）く してください」と 言（い）ったら、思（おも）ったより ずいぶん 短く なって しまった。でも、美容師（びようし）さんが 「似合（にあ）っていますよ」と 言ってくれたので、うれしかった。次（つぎ）は もっと くわしく 伝（つた）えられるように なりたい。</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Today I went to a hair salon alone for the first time. Explaining my hairstyle in Japanese was nerve-racking. When I said 'a little shorter, please,' it came out much shorter than I expected. But the stylist said 'It suits you,' so I was happy. Next time I want to explain in more detail.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>はじめて 一人で／〜てしまった／似合っています</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>体験＋気持ちの流れ（日常）。</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>カイの小さな成長。</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>1話者・カイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>L-013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>カイのストーリー</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>カイのつぶやき：好きな食べ物</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>一人称</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>ちょっと 休憩（きゅうけい）。みなさん、こんにちは、カイです。今日（きょう）は ぼくの 好（す）きな 食（た）べ物（もの）の 話（はなし）。実（じつ）は、ぼくは おにぎりが 大好（だいす）きです。コンビニの おにぎりも おいしいけれど、自分（じぶん）で 作（つく）るのも 楽（たの）しいです。みなさんの 好きな 日本（にほん）の 食べ物は 何（なん）ですか？</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>A little break. Hi everyone, it's Kai. Today, a chat about my favorite food. Actually, I love onigiri (rice balls). Convenience-store onigiri are tasty, but making them myself is fun too. What's your favorite Japanese food?</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>ちょっと 休憩／実は／〜は 何ですか？</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>カイの語りかけ・気軽な小ネタ（休憩室）。</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>親近感・問いかけ。</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>1話者・カイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>L-014</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>昔話</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>桃太郎</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が 流（なが）れて きました。おばあさんが 桃を 切（き）ると、中（なか）から 元気（げんき）な 男（おとこ）の子（こ）が 生（う）まれました。名前（なまえ）を 桃太郎（ももたろう）と つけました。桃太郎は 大（おお）きく なって、鬼（おに）を 退治（たいじ）しに 行くことに しました。</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Long ago, in a certain place, lived an old man and an old woman. One day, a big peach came floating down the river. When the old woman cut it open, a healthy boy was born from inside. They named him Momotaro. Momotaro grew up and decided to go defeat the ogres.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>むかしむかし／〜と いいました／〜ことに した</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>昔話の定型表現に親しむ。</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>有名な物語で親しみやすい。</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>1話者・語り</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>L-015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>怖い話</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>真夜中の水の音</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>夜中（よなか）、トイレに 起（お）きた。家（いえ）には 私（わたし）一人（ひとり）の はずだった。でも、台所（だいどころ）から 水（みず）の 音（おと）が 聞（き）こえる。だれかが 蛇口（じゃぐち）を 使（つか）っている…？こわごわ のぞくと、誰（だれ）も いない。ただ、コップに 水が いっぱい 入（はい）っていた。私（わたし）は 飲（の）んでいない。あの 水は、だれが…。</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>In the middle of the night, I got up for the toilet. I should have been alone in the house. But I heard the sound of water from the kitchen. Was someone using the faucet...? Fearfully I peeked in—no one. Just a glass full of water. I hadn't poured it. Who filled that glass...?</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>〜のはず／聞こえる／だれも いない</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>怪談の“間”と落ちを味わう。</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>ゾクッとする中毒性。</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>1話者・低めの声</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>L-016</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>文化と本音</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>本音講座</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>「大丈夫です」の正体</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>多義的な「大丈夫」を読み解く。</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>「え、両方!?」の発見＝SNS映え。</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>1話者・解説</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>L-017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>あるある</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>日本の電車は静か</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>〜と、〜／ほとんど 話しません／心地よい</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>文化比較の読み物。</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>「わかる!」共感で拡散。</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>L-018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>食べもの</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>ラーメンを食べよう</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>読み物</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>日本（にほん）に 来（き）たら、ぜひ ラーメンを 食（た）べてみてください。ラーメンには いろいろな 種類（しゅるい）が あります。しょうゆ、塩（しお）、みそ、とんこつ…。お店（みせ）に よって 味（あじ）が ちがいます。注文（ちゅうもん）の とき、「麺（めん）の かたさ」を 選（えら）べる 店（みせ）も あります。かたいのが 好（す）きなら「かため」と 言（い）いましょう。あなたの 好（す）きな ラーメンは どれですか。</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>When you come to Japan, definitely try ramen. There are many kinds: soy sauce, salt, miso, tonkotsu... The taste differs by shop. When ordering, some shops let you choose 'noodle firmness.' If you like it firm, say 'katame.' Which ramen is your favorite?</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>ぜひ 〜てみてください／〜によって／〜と 言いましょう</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>紹介＋注文の実用。</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>おいしそうで食欲がわく。</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -1854,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>怖い話</t>
+          <t>日本語ミステリー</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>真夜中の水の音</t>
+          <t>消えた駅弁の謎 第1話：駅で事件発生</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2969,40 +2969,40 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>夜中（よなか）、トイレに 起（お）きた。家（いえ）には 私（わたし）一人（ひとり）の はずだった。でも、台所（だいどころ）から 水（みず）の 音（おと）が 聞（き）こえる。だれかが 蛇口（じゃぐち）を 使（つか）っている…？こわごわ のぞくと、誰（だれ）も いない。ただ、コップに 水が いっぱい 入（はい）っていた。私（わたし）は 飲（の）んでいない。あの 水は、だれが…。</t>
+          <t>東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。朝（あさ）、店（みせ）を 開（あ）けると、一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が 10個（こ）、消（き）えていたのだ。店長（てんちょう）は あわてて 駅員（えきいん）の 田中（たなか）さんに 相談（そうだん）した。「鍵（かぎ）は かかっていたのに、どうして…？」田中さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>In the middle of the night, I got up for the toilet. I should have been alone in the house. But I heard the sound of water from the kitchen. Was someone using the faucet...? Fearfully I peeked in—no one. Just a glass full of water. I hadn't poured it. Who filled that glass...?</t>
+          <t>An incident occurred at a famous ekiben (station bento) shop in Tokyo Station. In the morning, when they opened, 10 of the most popular 'Sea Bounty Bento' had vanished. The flustered manager consulted station attendant Tanaka. 'The door was locked, so how...?' Tanaka thought. This might not be an ordinary thief.</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>〜のはず／聞こえる／だれも いない</t>
+          <t>事件が 起きた／消えていた／〜かもしれない</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>怪談の“間”と落ちを味わう。</t>
+          <t>事件の発端を読む（密室の謎）。</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>ゾクッとする中毒性。</t>
+          <t>鍵がかかっていたのに消えた＝続きが気になる第1話。</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1話者・低めの声</t>
+          <t>1話者・語り(緊張感)</t>
         </is>
       </c>
     </row>
@@ -3019,60 +3019,60 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>本音講座</t>
+          <t>日本語ミステリー</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>「大丈夫です」の正体</t>
+          <t>消えた駅弁の謎 第2話：証言を聞く</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>解説</t>
+          <t>対話</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
+          <t>田中（たなか）さんは、店（みせ）の 近（ちか）くに いた 人（ひと）たちに 話（はなし）を 聞（き）いた。掃除（そうじ）の おばさん：「朝（あさ）5時（じ）ごろ、白（しろ）い 服（ふく）の 人を 見（み）ました」。となりの コーヒー店（てん）の 店員（てんいん）：「変（へん）な 音（おと）が しました」。でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。田中さんは 首（くび）を かしげた。「おかしいな…」</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
+          <t>Tanaka asked people who had been near the shop. Cleaning lady: 'Around 5 a.m., I saw someone in white clothes.' The neighboring coffee-shop clerk: 'There was a strange sound.' But the security camera showed no one. Tanaka tilted his head. 'Strange...'</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
+          <t>話を 聞いた／〜を 見ました／だれも 映っていない</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>多義的な「大丈夫」を読み解く。</t>
+          <t>証言の聞き取りと矛盾を読む。</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>「え、両方!?」の発見＝SNS映え。</t>
+          <t>目撃者はいるのにカメラに映らない＝謎が深まる。</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1話者・解説</t>
+          <t>多声TTS:刑事/証人たち</t>
         </is>
       </c>
     </row>
@@ -3089,60 +3089,60 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>あるある</t>
+          <t>日本語ミステリー</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>日本の電車は静か</t>
+          <t>消えた駅弁の謎 第3話：容疑者登場</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>読み物</t>
+          <t>対話</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
+          <t>次（つぎ）の 日（ひ）、田中（たなか）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。男は 駅（えき）の 清掃員（せいそういん）だった。「あの 朝（あさ）、何（なに）を していましたか」。男：「私（わたし）は ただ、ゴミを 集（あつ）めていただけです」。でも、男の カバンから、弁当（べんとう）の 包（つつ）み紙（がみ）が 落（お）ちた。田中さんの 目（め）が 光（ひか）った。「これは…？」</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
+          <t>The next day, Tanaka found the man in white—a station cleaner. 'What were you doing that morning?' Man: 'I was just collecting trash.' But a bento wrapper fell from his bag. Tanaka's eyes flashed. 'What's this...?'</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>〜と、〜／ほとんど 話しません／心地よい</t>
+          <t>容疑者／〜ていただけです／目が 光った</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>文化比較の読み物。</t>
+          <t>容疑者への質問と証拠を読む。</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>「わかる!」共感で拡散。</t>
+          <t>決定的証拠?＝犯人かの緊張。</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
+          <t>多声TTS:刑事/容疑者</t>
         </is>
       </c>
     </row>
@@ -3159,58 +3159,338 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>日本語ミステリー</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>消えた駅弁の謎 第4話：真犯人は？</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>田中（たなか）さんは 包（つつ）み紙（がみ）を よく 見（み）た。男（おとこ）：「それは 私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！」実（じつ）は、犯人（はんにん）は 人（ひと）では なかった。防犯（ぼうはん）カメラを もう一度（いちど）見（み）ると、屋根（やね）の すきまから、大（おお）きな カラスが 弁当（べんとう）を 運（はこ）んでいた！みんな 大笑（おおわら）い。「鍵（かぎ）の 謎（なぞ）は、小（ちい）さな 窓（まど）だったのか」。事件（じけん）は 無事（ぶじ）解決（かいけつ）した。</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Tanaka looked closely at the wrapper. Man: 'That's trash I picked up. It's true!' In fact, the culprit wasn't a person. Watching the camera again—through a gap in the roof, a big crow was carrying the bento! Everyone burst out laughing. 'So the locked-room mystery was a small window.' The case was happily solved.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>よく 見た／実は／無事 解決した</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>真相・どんでん返しを読む。</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>犯人はカラス＝意外な落ちでスッキリ。</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:刑事/容疑者</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>L-019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>怖い話</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>真夜中の水の音</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>夜中（よなか）、トイレに 起（お）きた。家（いえ）には 私（わたし）一人（ひとり）の はずだった。でも、台所（だいどころ）から 水（みず）の 音（おと）が 聞（き）こえる。だれかが 蛇口（じゃぐち）を 使（つか）っている…？こわごわ のぞくと、誰（だれ）も いない。ただ、コップに 水が いっぱい 入（はい）っていた。私（わたし）は 飲（の）んでいない。あの 水は、だれが…。</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>In the middle of the night, I got up for the toilet. I should have been alone in the house. But I heard the sound of water from the kitchen. Was someone using the faucet...? Fearfully I peeked in—no one. Just a glass full of water. I hadn't poured it. Who filled that glass...?</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>〜のはず／聞こえる／だれも いない</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>怪談の“間”と落ちを味わう。</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>ゾクッとする中毒性。</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>1話者・低めの声</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>L-020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>文化と本音</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>本音講座</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>「大丈夫です」の正体</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>多義的な「大丈夫」を読み解く。</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>「え、両方!?」の発見＝SNS映え。</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>1話者・解説</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>L-021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>あるある</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>日本の電車は静か</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>〜と、〜／ほとんど 話しません／心地よい</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>文化比較の読み物。</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>「わかる!」共感で拡散。</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>L-022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>食べもの</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>ラーメンを食べよう</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>読み物</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>日本（にほん）に 来（き）たら、ぜひ ラーメンを 食（た）べてみてください。ラーメンには いろいろな 種類（しゅるい）が あります。しょうゆ、塩（しお）、みそ、とんこつ…。お店（みせ）に よって 味（あじ）が ちがいます。注文（ちゅうもん）の とき、「麺（めん）の かたさ」を 選（えら）べる 店（みせ）も あります。かたいのが 好（す）きなら「かため」と 言（い）いましょう。あなたの 好（す）きな ラーメンは どれですか。</t>
         </is>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I23" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>When you come to Japan, definitely try ramen. There are many kinds: soy sauce, salt, miso, tonkotsu... The taste differs by shop. When ordering, some shops let you choose 'noodle firmness.' If you like it firm, say 'katame.' Which ramen is your favorite?</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>ぜひ 〜てみてください／〜によって／〜と 言いましょう</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>紹介＋注文の実用。</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>おいしそうで食欲がわく。</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -1854,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3299,22 +3299,22 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>本音講座</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>「大丈夫です」の正体</t>
+          <t>カップラーメンの誕生</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>解説</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3324,35 +3324,37 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
+          <t>戦後（せんご）の 日本（にほん）。食（た）べ物（もの）が 少（すく）なく、人々（ひとびと）は 困（こま）っていた。一人（ひとり）の 男（おとこ）、安藤（あんどう）さんは 考（かんが）えた。「お湯（ゆ）を 入（い）れるだけで 食べられる めんを 作（つく）れないか」。
+毎日（まいにち）、朝（あさ）から 夜（よる）まで 研究（けんきゅう）した。何度（なんど）も 失敗（しっぱい）した。でも、あきらめなかった。ある日（ひ）、妻（つま）が 作る 天（てん）ぷらを 見（み）て、ひらめいた。「油（あぶら）で あげれば、めんが かわく！」
+こうして、世界（せかい）で はじめての インスタントラーメンが 生（う）まれた。今（いま）では、世界中（せかいじゅう）で 一年（いちねん）に 1000億（おく）食（しょく）も 食べられている。小（ちい）さな ひらめきが、世界を 変（か）えたのだ。</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
+          <t>Postwar Japan. Food was scarce and people were struggling. One man, Mr. Ando, thought: 'Couldn't I make noodles you can eat just by adding hot water?' Every day, from morning to night, he researched. He failed many times. But he never gave up. One day, watching his wife make tempura, it hit him: 'If you fry them in oil, the noodles dry out!' Thus the world's first instant ramen was born. Today, 100 billion servings are eaten worldwide each year. A small spark of insight changed the world.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
+          <t>あきらめなかった／ひらめいた／世界を 変えた</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>多義的な「大丈夫」を読み解く。</t>
+          <t>困難→挑戦→転機→成功 の物語の流れを聞く。</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>「え、両方!?」の発見＝SNS映え。</t>
+          <t>身近なカップ麺の“感動の誕生秘話”＝あこがれ・記憶に残る。</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1話者・解説</t>
+          <t>1話者・ナレーション(語り)</t>
         </is>
       </c>
     </row>
@@ -3374,55 +3376,55 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>あるある</t>
+          <t>本音講座</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>日本の電車は静か</t>
+          <t>「大丈夫です」の正体</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>読み物</t>
+          <t>解説</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
+          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
+          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>〜と、〜／ほとんど 話しません／心地よい</t>
+          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>文化比較の読み物。</t>
+          <t>多義的な「大丈夫」を読み解く。</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>「わかる!」共感で拡散。</t>
+          <t>「え、両方!?」の発見＝SNS映え。</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
+          <t>1話者・解説</t>
         </is>
       </c>
     </row>
@@ -3444,53 +3446,123 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
+          <t>あるある</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>日本の電車は静か</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>〜と、〜／ほとんど 話しません／心地よい</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>文化比較の読み物。</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>「わかる!」共感で拡散。</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>L-023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
           <t>食べもの</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>ラーメンを食べよう</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>読み物</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>日本（にほん）に 来（き）たら、ぜひ ラーメンを 食（た）べてみてください。ラーメンには いろいろな 種類（しゅるい）が あります。しょうゆ、塩（しお）、みそ、とんこつ…。お店（みせ）に よって 味（あじ）が ちがいます。注文（ちゅうもん）の とき、「麺（めん）の かたさ」を 選（えら）べる 店（みせ）も あります。かたいのが 好（す）きなら「かため」と 言（い）いましょう。あなたの 好（す）きな ラーメンは どれですか。</t>
         </is>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I24" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>When you come to Japan, definitely try ramen. There are many kinds: soy sauce, salt, miso, tonkotsu... The taste differs by shop. When ordering, some shops let you choose 'noodle firmness.' If you like it firm, say 'katame.' Which ramen is your favorite?</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>ぜひ 〜てみてください／〜によって／〜と 言いましょう</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>紹介＋注文の実用。</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>おいしそうで食欲がわく。</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -773,20 +773,20 @@
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>行員（こういん）：いらっしゃいませ。本日（ほんじつ）は どのような ご用件（ようけん）ですか。
-グエン：口座（こうざ）を 作（つく）りたいんですが。
+カイ：口座（こうざ）を 作（つく）りたいんですが。
 行員：ありがとうございます。在留（ざいりゅう）カードと、印鑑（いんかん）か サインは ご用意（ようい）できますか。
-グエン：印鑑は ありませんが、サインでも いいですか。
+カイ：印鑑は ありませんが、サインでも いいですか。
 行員：はい、大丈夫（だいじょうぶ）です。では、こちらの 用紙（ようし）に お名前（なまえ）と ご住所（じゅうしょ）を ご記入（きにゅう）ください。
-グエン：書（か）けました。
+カイ：書（か）けました。
 行員：ありがとうございます。10分（ぷん）ほどで お作（つく）りします。</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Teller: Welcome. How may I help you today? / Guen: I'd like to open an account. / Teller: Thank you. Do you have your residence card and a seal (hanko) or signature? / Guen: I don't have a seal—is a signature okay? / Teller: Yes, that's fine. Please fill in your name and address on this form. / Guen: Done. / Teller: Thank you. It'll be ready in about 10 minutes.</t>
+          <t>Teller: Welcome. How may I help you today? / Kai: I'd like to open an account. / Teller: Thank you. Do you have your residence card and a seal (hanko) or signature? / Kai: I don't have a seal—is a signature okay? / Teller: Yes, that's fine. Please fill in your name and address on this form. / Kai: Done. / Teller: Thank you. It'll be ready in about 10 minutes.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -849,19 +849,19 @@
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>職員（しょくいん）：こんにちは。ご用件（ようけん）は 何（なん）でしょうか。
-ラフィ：先月（せんげつ）引（ひ）っ越（こ）してきたので、転入（てんにゅう）の 手続（てつづ）きを したいです。
+カイ：先月（せんげつ）引（ひ）っ越（こ）してきたので、転入（てんにゅう）の 手続（てつづ）きを したいです。
 職員：かしこまりました。前（まえ）に 住（す）んでいた 市（し）で「転出届（てんしゅつとどけ）」は もらいましたか。
-ラフィ：はい、これです。
+カイ：はい、これです。
 職員：ありがとうございます。在留（ざいりゅう）カードも お預（あず）かりします。…はい、住所（じゅうしょ）を 変更（へんこう）しました。国民健康保険（こくみんけんこうほけん）も 一緒（いっしょ）に できますが、いかがですか。
-ラフィ：はい、お願（ねが）いします。</t>
+カイ：はい、お願（ねが）いします。</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Clerk: Hello, how can I help? / Rafi: I moved last month, so I'd like to do the moving-in procedure. / Clerk: Certainly. Did you get a 'moving-out certificate' from your previous city? / Rafi: Yes, here it is. / Clerk: Thank you. I'll take your residence card too. ...Done, your address is updated. We can also do national health insurance now—would you like that? / Rafi: Yes, please.</t>
+          <t>Clerk: Hello, how can I help? / Kai: I moved last month, so I'd like to do the moving-in procedure. / Clerk: Certainly. Did you get a 'moving-out certificate' from your previous city? / Kai: Yes, here it is. / Clerk: Thank you. I'll take your residence card too. ...Done, your address is updated. We can also do national health insurance now—would you like that? / Kai: Yes, please.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1001,11 +1001,11 @@
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>店員：いらっしゃいませ。お部屋（へや）を お探（さが）しですか。
-リン：はい。駅（えき）から 近くて、家賃（やちん）は 6万円（まんえん）まで が いいです。
+カイ：はい。駅（えき）から 近くて、家賃（やちん）は 6万円（まんえん）まで が いいです。
 店員：ペットは 飼（か）われますか。
-リン：いいえ、飼いません。
+カイ：いいえ、飼いません。
 店員：では、こちらは いかがですか。駅から 歩（ある）いて 5分（ふん）、家賃 5万8千円（まんはっせん）です。
-リン：いいですね。中（なか）を 見（み）られますか。
+カイ：いいですね。中（なか）を 見（み）られますか。
 店員：はい。今（いま）から ご案内（あんない）できます。</t>
         </is>
       </c>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Agent: Welcome. Looking for a room? / Rin: Yes. Near the station, rent up to 60,000 yen. / Agent: Will you keep pets? / Rin: No. / Agent: Then how about this? 5 min walk from the station, 58,000 yen. / Rin: Nice. Can I see inside? / Agent: Yes, I can show you now.</t>
+          <t>Agent: Welcome. Looking for a room? / Kai: Yes. Near the station, rent up to 60,000 yen. / Agent: Will you keep pets? / Kai: No. / Agent: Then how about this? 5 min walk from the station, 58,000 yen. / Kai: Nice. Can I see inside? / Agent: Yes, I can show you now.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1227,11 +1227,11 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>リン：すみません、横浜（よこはま）へ 行きたいんですが、どう 行けば いいですか。
+          <t>カイ：すみません、横浜（よこはま）へ 行きたいんですが、どう 行けば いいですか。
 駅員：横浜ですね。3番線（ばんせん）の 電車に 乗（の）って、品川（しながわ）で 乗り換（か）えてください。
-リン：ありがとうございます。あ、電車は 遅（おく）れていますか。
+カイ：ありがとうございます。あ、電車は 遅（おく）れていますか。
 駅員：はい、事故（じこ）の 影響（えいきょう）で、10分（ぷん）ほど 遅れています。
-リン：急（いそ）いでいるので、ほかの 行き方（かた）は ありますか。
+カイ：急（いそ）いでいるので、ほかの 行き方（かた）は ありますか。
 駅員：バスも ありますが、電車の ほうが 早（はや）いと 思います。</t>
         </is>
       </c>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Rin: Excuse me, I want to go to Yokohama—how do I get there? / Staff: Yokohama? Take the train on track 3 and change at Shinagawa. / Rin: Thanks. Are the trains delayed? / Staff: Yes, about 10 minutes due to an accident. / Rin: I'm in a hurry—is there another way? / Staff: There's a bus, but the train is faster.</t>
+          <t>Kai: Excuse me, I want to go to Yokohama—how do I get there? / Staff: Yokohama? Take the train on track 3 and change at Shinagawa. / Kai: Thanks. Are the trains delayed? / Staff: Yes, about 10 minutes due to an accident. / Kai: I'm in a hurry—is there another way? / Staff: There's a bus, but the train is faster.</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>リン：すみません、道（みち）に 迷（まよ）って しまって…。この 住所（じゅうしょ）に 行きたいんです。
+          <t>カイ：すみません、道（みち）に 迷（まよ）って しまって…。この 住所（じゅうしょ）に 行きたいんです。
 警官（けいかん）：どれどれ。ああ、ここですね。この 道を まっすぐ 行って、二（ふた）つ目（め）の 信号（しんごう）を 左（ひだり）です。
-リン：二つ目の 信号を 左ですね。
+カイ：二つ目の 信号を 左ですね。
 警官：はい。そこから 歩（ある）いて 3分（ぷん）くらいです。
-リン：ありがとうございます。助（たす）かりました。</t>
+カイ：ありがとうございます。助（たす）かりました。</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Rin: Excuse me, I'm lost... I want to go to this address. / Officer: Let me see. Ah, here. Go straight on this road and turn left at the second light. / Rin: Left at the second light. / Officer: Yes. About a 3-minute walk from there. / Rin: Thank you, that helps.</t>
+          <t>Kai: Excuse me, I'm lost... I want to go to this address. / Officer: Let me see. Ah, here. Go straight on this road and turn left at the second light. / Kai: Left at the second light. / Officer: Yes. About a 3-minute walk from there. / Kai: Thank you, that helps.</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -1377,19 +1377,19 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>店員：ご契約（けいやく）ですね。在留（ざいりゅう）カードと、お支払（しはら）い方法（ほうほう）は 何（なに）に なさいますか。
-ラフィ：クレジットカードで お願（ねが）いします。一番（いちばん）安（やす）い プランが いいです。
+カイ：クレジットカードで お願（ねが）いします。一番（いちばん）安（やす）い プランが いいです。
 店員：では、こちらが 月（つき）2,980円（えん）で、データは 20ギガ 使（つか）えます。
-ラフィ：電話（でんわ）も できますか。
+カイ：電話（でんわ）も できますか。
 店員：はい、5分（ふん）までの 通話（つうわ）は 無料（むりょう）です。
-ラフィ：いいですね。それに します。</t>
+カイ：いいですね。それに します。</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Clerk: Signing up, right? Your residence card, and how will you pay? / Rafi: By credit card, please. I'd like the cheapest plan. / Clerk: Then this one is 2,980 yen a month with 20 GB of data. / Rafi: Can I make calls too? / Clerk: Yes, calls up to 5 minutes are free. / Rafi: Nice. I'll take it.</t>
+          <t>Clerk: Signing up, right? Your residence card, and how will you pay? / Kai: By credit card, please. I'd like the cheapest plan. / Clerk: Then this one is 2,980 yen a month with 20 GB of data. / Kai: Can I make calls too? / Clerk: Yes, calls up to 5 minutes are free. / Kai: Nice. I'll take it.</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1661,40 +1661,40 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>解説</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>きょうの ことばは「ふわふわ」です。やわらかくて、かるい ものの ことです。たとえば、「この パンは ふわふわです」。くもや、ねこの けも ふわふわ。さわると きもちが いいですね。</t>
+          <t>今日（きょう）の ことばは「ふわふわ」です。やわらかくて 軽（かる）い ようすを 表（あらわ）します。たとえば、焼（や）きたての パンは「ふわふわ」、空（そら）に うかぶ 雲（くも）も「ふわふわ」、猫（ねこ）の 毛（け）も「ふわふわ」です。物（もの）だけでなく、気持（きも）ちにも 使（つか）えます。うれしくて 心（こころ）が 軽い ときは「気持ちが ふわふわする」と 言（い）います。日本語（にほんご）には こんな 音（おと）の 言葉（オノマトペ）が たくさん あって、使うと 表現（ひょうげん）が ぐっと 生（い）き生（い）きします。みなさんも 今日 ひとつ 使ってみませんか。</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Today's word is 'fuwafuwa.' It means something soft and light. For example, 'This bread is fuwafuwa.' Clouds and a cat's fur are fuwafuwa too. They feel nice to touch.</t>
+          <t>Today's word is 'fuwafuwa.' It describes something soft and light. For example, freshly baked bread is 'fuwafuwa,' clouds floating in the sky are 'fuwafuwa,' and a cat's fur is 'fuwafuwa.' It works for feelings too, not just objects. When you're happy and your heart feels light, you say 'my heart feels fuwafuwa.' Japanese has many of these sound-words (onomatopoeia), and using them makes your expression much more vivid. Why not try using one today?</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>ふわふわ(=soft &amp; fluffy)／やわらかい／さわると きもちがいい</t>
+          <t>ふわふわ(=soft &amp; light)／気持ちが ふわふわする／オノマトペ</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>オノマトペ「ふわふわ」の意味と使い方。</t>
+          <t>擬音語の意味と、物・気持ち両方への使い方。</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>音がかわいくて覚えやすい。</t>
+          <t>使うと表現が生き生き＝今日ひとつ使ってみたくなる。</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1840,6 +1840,216 @@
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>1話者・解説</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>S-017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>本音講座</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>「大丈夫です」の正体</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>多義的な「大丈夫」を読み解く。</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>「え、両方!?」の発見＝SNS映え。</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>1話者・解説</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>S-018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>あるある</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>日本の電車は静か</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>〜と、〜／ほとんど 話しません／心地よい</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>文化比較の読み物。</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>「わかる!」共感で拡散。</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>S-019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>文化と本音</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>食べもの</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ラーメンを食べよう</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）に 来（き）たら、ぜひ ラーメンを 食（た）べてみてください。ラーメンには いろいろな 種類（しゅるい）が あります。しょうゆ、塩（しお）、みそ、とんこつ…。お店（みせ）に よって 味（あじ）が ちがいます。注文（ちゅうもん）の とき、「麺（めん）の かたさ」を 選（えら）べる 店（みせ）も あります。かたいのが 好（す）きなら「かため」と 言（い）いましょう。あなたの 好（す）きな ラーメンは どれですか。</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>When you come to Japan, definitely try ramen. There are many kinds: soy sauce, salt, miso, tonkotsu... The taste differs by shop. When ordering, some shops let you choose 'noodle firmness.' If you like it firm, say 'katame.' Which ramen is your favorite?</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>ぜひ 〜てみてください／〜によって／〜と 言いましょう</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>紹介＋注文の実用。</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>おいしそうで食欲がわく。</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2598,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ベトナムから来たグエンさん</t>
+          <t>ゲストのカイさん</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -2403,21 +2613,21 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>司会（しかい）：今日（きょう）の ゲストは、ベトナムから 来（き）た グエンさんです。日本（にほん）に 来て どのくらいですか。
-グエン：2年（ねん）です。
+          <t>司会（しかい）：今日（きょう）の ゲストは、日本（にほん）で 勉強（べんきょう）している カイさんです。日本に 来て どのくらいですか。
+カイ：2年（ねん）です。
 司会：日本で 一番（いちばん）好（す）きな ものは？
-グエン：温泉（おんせん）です。とても 気持（きも）ちが いいです。
+カイ：温泉（おんせん）です。とても 気持（きも）ちが いいです。
 司会：これから 何（なに）を したいですか。
-グエン：日本語（にほんご）を もっと 上手（じょうず）に なりたいです。
+カイ：日本語（にほんご）を もっと 上手（じょうず）に なりたいです。
 司会：いいですね！ がんばってください。</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Host: Today's guest is Guen from Vietnam. How long have you been in Japan? / Guen: Two years. / Host: What's your favorite thing in Japan? / Guen: Hot springs. They feel so good. / Host: What do you want to do from now on? / Guen: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
+          <t>Host: Today's guest is Kai, who is studying in Japan. How long have you been in Japan? / Kai: Two years. / Host: What's your favorite thing in Japan? / Kai: Hot springs. They feel so good. / Host: What do you want to do from now on? / Kai: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -2884,17 +3094,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>昔話</t>
+          <t>カイのストーリー</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>桃太郎</t>
+          <t>友だちができた</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>一人称</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2904,35 +3114,35 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が 流（なが）れて きました。おばあさんが 桃を 切（き）ると、中（なか）から 元気（げんき）な 男（おとこ）の子（こ）が 生（う）まれました。名前（なまえ）を 桃太郎（ももたろう）と つけました。桃太郎は 大（おお）きく なって、鬼（おに）を 退治（たいじ）しに 行くことに しました。</t>
+          <t>日本（にほん）に 来（き）て すぐは、友（とも）だちが いなくて さびしかった。でも、日本語（にほんご）の 教室（きょうしつ）で となりに 座（すわ）った 人（ひと）が、やさしく 話（はな）しかけて くれた。「いっしょに お昼（ひる）、食（た）べない？」その 一言（ひとこと）が とても うれしかった。今（いま）では、休（やす）みの 日（ひ）に いっしょに 出（で）かける 仲（なか）だ。勇気（ゆうき）を 出（だ）して よかった。</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Long ago, in a certain place, lived an old man and an old woman. One day, a big peach came floating down the river. When the old woman cut it open, a healthy boy was born from inside. They named him Momotaro. Momotaro grew up and decided to go defeat the ogres.</t>
+          <t>Right after I came to Japan, I had no friends and felt lonely. But in Japanese class, the person who sat next to me kindly spoke to me: 'Want to have lunch together?' That one phrase made me so happy. Now we're close enough to go out on days off. I'm glad I found the courage.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>むかしむかし／〜と いいました／〜ことに した</t>
+          <t>さびしかった／話しかけて くれた／勇気を 出して よかった</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>昔話の定型表現に親しむ。</t>
+          <t>友だち作りの体験と気持ち（日常）。</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>有名な物語で親しみやすい。</t>
+          <t>一歩ふみ出す勇気＝共感。</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1話者・語り</t>
+          <t>1話者・カイ</t>
         </is>
       </c>
     </row>
@@ -2954,17 +3164,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>日本語ミステリー</t>
+          <t>カイのストーリー</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第1話：駅で事件発生</t>
+          <t>お祭りに行く</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>一人称</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2974,35 +3184,35 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。朝（あさ）、店（みせ）を 開（あ）けると、一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が 10個（こ）、消（き）えていたのだ。店長（てんちょう）は あわてて 駅員（えきいん）の 田中（たなか）さんに 相談（そうだん）した。「鍵（かぎ）は かかっていたのに、どうして…？」田中さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
+          <t>夏（なつ）の 夜（よる）、はじめて 日本（にほん）の お祭（まつ）りに 行（い）った。たくさんの 人（ひと）が ゆかたを 着（き）ていて、とても きれいだった。屋台（やたい）で たこ焼（や）きと かき氷（ごおり）を 買（か）って 食（た）べた。最後（さいご）に 花火（はなび）が 上（あ）がった。大（おお）きな 音（おと）と 光（ひかり）に、胸（むね）が どきどきした。日本の 夏（なつ）は、わすれられない 思（おも）い出（で）に なった。</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>An incident occurred at a famous ekiben (station bento) shop in Tokyo Station. In the morning, when they opened, 10 of the most popular 'Sea Bounty Bento' had vanished. The flustered manager consulted station attendant Tanaka. 'The door was locked, so how...?' Tanaka thought. This might not be an ordinary thief.</t>
+          <t>On a summer night, I went to a Japanese festival for the first time. Many people wore yukata and looked beautiful. At the stalls I bought and ate takoyaki and shaved ice. At the end, fireworks went up. The loud sound and light made my heart race. Japan's summer became an unforgettable memory.</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>事件が 起きた／消えていた／〜かもしれない</t>
+          <t>はじめて／〜を 買って 食べた／わすれられない 思い出</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>事件の発端を読む（密室の謎）。</t>
+          <t>お祭りの描写＋感動（旅行・季節）。</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>鍵がかかっていたのに消えた＝続きが気になる第1話。</t>
+          <t>夏祭りの高揚・五感で楽しい。</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1話者・語り(緊張感)</t>
+          <t>1話者・カイ</t>
         </is>
       </c>
     </row>
@@ -3024,17 +3234,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>日本語ミステリー</t>
+          <t>昔話</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第2話：証言を聞く</t>
+          <t>桃太郎</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>対話</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3044,35 +3254,35 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>田中（たなか）さんは、店（みせ）の 近（ちか）くに いた 人（ひと）たちに 話（はなし）を 聞（き）いた。掃除（そうじ）の おばさん：「朝（あさ）5時（じ）ごろ、白（しろ）い 服（ふく）の 人を 見（み）ました」。となりの コーヒー店（てん）の 店員（てんいん）：「変（へん）な 音（おと）が しました」。でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。田中さんは 首（くび）を かしげた。「おかしいな…」</t>
+          <t>むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が 流（なが）れて きました。おばあさんが 桃を 切（き）ると、中（なか）から 元気（げんき）な 男（おとこ）の子（こ）が 生（う）まれました。名前（なまえ）を 桃太郎（ももたろう）と つけました。桃太郎は 大（おお）きく なって、鬼（おに）を 退治（たいじ）しに 行くことに しました。</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Tanaka asked people who had been near the shop. Cleaning lady: 'Around 5 a.m., I saw someone in white clothes.' The neighboring coffee-shop clerk: 'There was a strange sound.' But the security camera showed no one. Tanaka tilted his head. 'Strange...'</t>
+          <t>Long ago, in a certain place, lived an old man and an old woman. One day, a big peach came floating down the river. When the old woman cut it open, a healthy boy was born from inside. They named him Momotaro. Momotaro grew up and decided to go defeat the ogres.</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>話を 聞いた／〜を 見ました／だれも 映っていない</t>
+          <t>むかしむかし／〜と いいました／〜ことに した</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>証言の聞き取りと矛盾を読む。</t>
+          <t>昔話の定型表現に親しむ。</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>目撃者はいるのにカメラに映らない＝謎が深まる。</t>
+          <t>有名な物語で親しみやすい。</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:刑事/証人たち</t>
+          <t>1話者・語り</t>
         </is>
       </c>
     </row>
@@ -3099,50 +3309,50 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第3話：容疑者登場</t>
+          <t>消えた駅弁の謎 第1話：駅で事件発生</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>対話</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>次（つぎ）の 日（ひ）、田中（たなか）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。男は 駅（えき）の 清掃員（せいそういん）だった。「あの 朝（あさ）、何（なに）を していましたか」。男：「私（わたし）は ただ、ゴミを 集（あつ）めていただけです」。でも、男の カバンから、弁当（べんとう）の 包（つつ）み紙（がみ）が 落（お）ちた。田中さんの 目（め）が 光（ひか）った。「これは…？」</t>
+          <t>東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。朝（あさ）、店（みせ）を 開（あ）けると、一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が 10個（こ）、消（き）えていたのだ。店長（てんちょう）は あわてて 駅員（えきいん）の 田中（たなか）さんに 相談（そうだん）した。「鍵（かぎ）は かかっていたのに、どうして…？」田中さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>The next day, Tanaka found the man in white—a station cleaner. 'What were you doing that morning?' Man: 'I was just collecting trash.' But a bento wrapper fell from his bag. Tanaka's eyes flashed. 'What's this...?'</t>
+          <t>An incident occurred at a famous ekiben (station bento) shop in Tokyo Station. In the morning, when they opened, 10 of the most popular 'Sea Bounty Bento' had vanished. The flustered manager consulted station attendant Tanaka. 'The door was locked, so how...?' Tanaka thought. This might not be an ordinary thief.</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>容疑者／〜ていただけです／目が 光った</t>
+          <t>事件が 起きた／消えていた／〜かもしれない</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>容疑者への質問と証拠を読む。</t>
+          <t>事件の発端を読む（密室の謎）。</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>決定的証拠?＝犯人かの緊張。</t>
+          <t>鍵がかかっていたのに消えた＝続きが気になる第1話。</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:刑事/容疑者</t>
+          <t>1話者・語り(緊張感)</t>
         </is>
       </c>
     </row>
@@ -3169,50 +3379,50 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第4話：真犯人は？</t>
+          <t>消えた駅弁の謎 第2話：証言を聞く</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>対話</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>田中（たなか）さんは 包（つつ）み紙（がみ）を よく 見（み）た。男（おとこ）：「それは 私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！」実（じつ）は、犯人（はんにん）は 人（ひと）では なかった。防犯（ぼうはん）カメラを もう一度（いちど）見（み）ると、屋根（やね）の すきまから、大（おお）きな カラスが 弁当（べんとう）を 運（はこ）んでいた！みんな 大笑（おおわら）い。「鍵（かぎ）の 謎（なぞ）は、小（ちい）さな 窓（まど）だったのか」。事件（じけん）は 無事（ぶじ）解決（かいけつ）した。</t>
+          <t>田中（たなか）さんは、店（みせ）の 近（ちか）くに いた 人（ひと）たちに 話（はなし）を 聞（き）いた。掃除（そうじ）の おばさん：「朝（あさ）5時（じ）ごろ、白（しろ）い 服（ふく）の 人を 見（み）ました」。となりの コーヒー店（てん）の 店員（てんいん）：「変（へん）な 音（おと）が しました」。でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。田中さんは 首（くび）を かしげた。「おかしいな…」</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Tanaka looked closely at the wrapper. Man: 'That's trash I picked up. It's true!' In fact, the culprit wasn't a person. Watching the camera again—through a gap in the roof, a big crow was carrying the bento! Everyone burst out laughing. 'So the locked-room mystery was a small window.' The case was happily solved.</t>
+          <t>Tanaka asked people who had been near the shop. Cleaning lady: 'Around 5 a.m., I saw someone in white clothes.' The neighboring coffee-shop clerk: 'There was a strange sound.' But the security camera showed no one. Tanaka tilted his head. 'Strange...'</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>よく 見た／実は／無事 解決した</t>
+          <t>話を 聞いた／〜を 見ました／だれも 映っていない</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>真相・どんでん返しを読む。</t>
+          <t>証言の聞き取りと矛盾を読む。</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>犯人はカラス＝意外な落ちでスッキリ。</t>
+          <t>目撃者はいるのにカメラに映らない＝謎が深まる。</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:刑事/容疑者</t>
+          <t>多声TTS:刑事/証人たち</t>
         </is>
       </c>
     </row>
@@ -3234,17 +3444,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>怖い話</t>
+          <t>日本語ミステリー</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>真夜中の水の音</t>
+          <t>消えた駅弁の謎 第3話：容疑者登場</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>対話</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3254,35 +3464,35 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>夜中（よなか）、トイレに 起（お）きた。家（いえ）には 私（わたし）一人（ひとり）の はずだった。でも、台所（だいどころ）から 水（みず）の 音（おと）が 聞（き）こえる。だれかが 蛇口（じゃぐち）を 使（つか）っている…？こわごわ のぞくと、誰（だれ）も いない。ただ、コップに 水が いっぱい 入（はい）っていた。私（わたし）は 飲（の）んでいない。あの 水は、だれが…。</t>
+          <t>次（つぎ）の 日（ひ）、田中（たなか）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。男は 駅（えき）の 清掃員（せいそういん）だった。「あの 朝（あさ）、何（なに）を していましたか」。男：「私（わたし）は ただ、ゴミを 集（あつ）めていただけです」。でも、男の カバンから、弁当（べんとう）の 包（つつ）み紙（がみ）が 落（お）ちた。田中さんの 目（め）が 光（ひか）った。「これは…？」</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>In the middle of the night, I got up for the toilet. I should have been alone in the house. But I heard the sound of water from the kitchen. Was someone using the faucet...? Fearfully I peeked in—no one. Just a glass full of water. I hadn't poured it. Who filled that glass...?</t>
+          <t>The next day, Tanaka found the man in white—a station cleaner. 'What were you doing that morning?' Man: 'I was just collecting trash.' But a bento wrapper fell from his bag. Tanaka's eyes flashed. 'What's this...?'</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>〜のはず／聞こえる／だれも いない</t>
+          <t>容疑者／〜ていただけです／目が 光った</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>怪談の“間”と落ちを味わう。</t>
+          <t>容疑者への質問と証拠を読む。</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>ゾクッとする中毒性。</t>
+          <t>決定的証拠?＝犯人かの緊張。</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1話者・低めの声</t>
+          <t>多声TTS:刑事/容疑者</t>
         </is>
       </c>
     </row>
@@ -3304,197 +3514,197 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
+          <t>日本語ミステリー</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>消えた駅弁の謎 第4話：真犯人は？</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>田中（たなか）さんは 包（つつ）み紙（がみ）を よく 見（み）た。男（おとこ）：「それは 私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！」実（じつ）は、犯人（はんにん）は 人（ひと）では なかった。防犯（ぼうはん）カメラを もう一度（いちど）見（み）ると、屋根（やね）の すきまから、大（おお）きな カラスが 弁当（べんとう）を 運（はこ）んでいた！みんな 大笑（おおわら）い。「鍵（かぎ）の 謎（なぞ）は、小（ちい）さな 窓（まど）だったのか」。事件（じけん）は 無事（ぶじ）解決（かいけつ）した。</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Tanaka looked closely at the wrapper. Man: 'That's trash I picked up. It's true!' In fact, the culprit wasn't a person. Watching the camera again—through a gap in the roof, a big crow was carrying the bento! Everyone burst out laughing. 'So the locked-room mystery was a small window.' The case was happily solved.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>よく 見た／実は／無事 解決した</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>真相・どんでん返しを読む。</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>犯人はカラス＝意外な落ちでスッキリ。</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:刑事/容疑者</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>L-021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>怖い話</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>真夜中の水の音</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>夜中（よなか）、トイレに 起（お）きた。家（いえ）には 私（わたし）一人（ひとり）の はずだった。でも、台所（だいどころ）から 水（みず）の 音（おと）が 聞（き）こえる。だれかが 蛇口（じゃぐち）を 使（つか）っている…？こわごわ のぞくと、誰（だれ）も いない。ただ、コップに 水が いっぱい 入（はい）っていた。私（わたし）は 飲（の）んでいない。あの 水は、だれが…。</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>In the middle of the night, I got up for the toilet. I should have been alone in the house. But I heard the sound of water from the kitchen. Was someone using the faucet...? Fearfully I peeked in—no one. Just a glass full of water. I hadn't poured it. Who filled that glass...?</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>〜のはず／聞こえる／だれも いない</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>怪談の“間”と落ちを味わう。</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>ゾクッとする中毒性。</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>1話者・低めの声</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>L-022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>カップラーメンの誕生</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>戦後（せんご）の 日本（にほん）。食（た）べ物（もの）が 少（すく）なく、人々（ひとびと）は 困（こま）っていた。一人（ひとり）の 男（おとこ）、安藤（あんどう）さんは 考（かんが）えた。「お湯（ゆ）を 入（い）れるだけで 食べられる めんを 作（つく）れないか」。
 毎日（まいにち）、朝（あさ）から 夜（よる）まで 研究（けんきゅう）した。何度（なんど）も 失敗（しっぱい）した。でも、あきらめなかった。ある日（ひ）、妻（つま）が 作る 天（てん）ぷらを 見（み）て、ひらめいた。「油（あぶら）で あげれば、めんが かわく！」
 こうして、世界（せかい）で はじめての インスタントラーメンが 生（う）まれた。今（いま）では、世界中（せかいじゅう）で 一年（いちねん）に 1000億（おく）食（しょく）も 食べられている。小（ちい）さな ひらめきが、世界を 変（か）えたのだ。</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I23" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Postwar Japan. Food was scarce and people were struggling. One man, Mr. Ando, thought: 'Couldn't I make noodles you can eat just by adding hot water?' Every day, from morning to night, he researched. He failed many times. But he never gave up. One day, watching his wife make tempura, it hit him: 'If you fry them in oil, the noodles dry out!' Thus the world's first instant ramen was born. Today, 100 billion servings are eaten worldwide each year. A small spark of insight changed the world.</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>あきらめなかった／ひらめいた／世界を 変えた</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>困難→挑戦→転機→成功 の物語の流れを聞く。</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>身近なカップ麺の“感動の誕生秘話”＝あこがれ・記憶に残る。</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>1話者・ナレーション(語り)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>L-021</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>文化と本音</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>本音講座</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>「大丈夫です」の正体</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>解説</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>日本語（にほんご）の「大丈夫（だいじょうぶ）です」は、便利（べんり）ですが、少（すこ）し ふくざつです。「コーヒー、いかがですか」「あ、大丈夫です」。これは「いりません」という 意味（いみ）です。でも、「明日（あした）、来（こ）られますか」「大丈夫です」なら「行（い）けます」という 意味。同（おな）じ 言葉（ことば）でも、場面（ばめん）で 意味が 変（か）わります。困（こま）ったら、相手（あいて）の 顔（かお）を 見（み）て 確認（かくにん）しましょう。</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Japanese 'daijoubu desu' is handy but a bit complex. 'Would you like coffee?' 'Oh, daijoubu desu.' Here it means 'No thanks.' But 'Can you come tomorrow?' 'Daijoubu desu' means 'I can go.' The same words change meaning by situation. If unsure, check the other person's face.</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>大丈夫です(=No thanks / OK)／場面で 意味が 変わる</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>多義的な「大丈夫」を読み解く。</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>「え、両方!?」の発見＝SNS映え。</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>1話者・解説</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>L-022</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>文化と本音</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>あるある</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>日本の電車は静か</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>読み物</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>日本（にほん）の 電車（でんしゃ）に 乗（の）ると、おどろくことが あります。とても 静（しず）かなのです。みんな スマホを 見（み）たり、寝（ね）たり して、ほとんど 話（はな）しません。電話（でんわ）も マナーモードです。最初（さいしょ）は さびしく 感（かん）じましたが、今（いま）は その 静かさが 心地（ここち）よいです。みなさんの 国（くに）の 電車は どうですか。</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>When you ride a train in Japan, something may surprise you: it's very quiet. Everyone looks at their phone or sleeps, and hardly anyone talks. Phones are on silent mode. At first I felt it was lonely, but now I find that quietness pleasant. What are trains like in your country?</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>〜と、〜／ほとんど 話しません／心地よい</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>文化比較の読み物。</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>「わかる!」共感で拡散。</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>1話者・朗読</t>
         </is>
       </c>
     </row>
@@ -3511,60 +3721,62 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>食べもの</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>ラーメンを食べよう</t>
+          <t>はやぶさの帰還</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>読み物</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>日本（にほん）に 来（き）たら、ぜひ ラーメンを 食（た）べてみてください。ラーメンには いろいろな 種類（しゅるい）が あります。しょうゆ、塩（しお）、みそ、とんこつ…。お店（みせ）に よって 味（あじ）が ちがいます。注文（ちゅうもん）の とき、「麺（めん）の かたさ」を 選（えら）べる 店（みせ）も あります。かたいのが 好（す）きなら「かため」と 言（い）いましょう。あなたの 好（す）きな ラーメンは どれですか。</t>
+          <t>「はやぶさ」という 小（ちい）さな 宇宙船（うちゅうせん）の 話（はなし）です。はやぶさは、地球（ちきゅう）から 遠（とお）い 小惑星（しょうわくせい）まで 行（い）き、石（いし）を 取（と）って 帰（かえ）る という 世界（せかい）で はじめての ミッションに 挑（いど）みました。
+旅（たび）の 途中（とちゅう）、機械（きかい）が 何度（なんど）も こわれ、通信（つうしん）も 切（き）れました。「もう だめか」と 多（おお）くの 人（ひと）が 思（おも）いました。でも、研究者（けんきゅうしゃ）たちは あきらめませんでした。
+7年（ねん）、60億（おく）キロの 旅（たび）の すえ、はやぶさは 地球に 戻（もど）りました。最後（さいご）は 自分（じぶん）は 燃（も）えながら、石（いし）の 入（はい）った カプセルだけを 送（おく）り届（とど）けたのです。その 姿（すがた）に、世界中（せかいじゅう）が 涙（なみだ）しました。</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>When you come to Japan, definitely try ramen. There are many kinds: soy sauce, salt, miso, tonkotsu... The taste differs by shop. When ordering, some shops let you choose 'noodle firmness.' If you like it firm, say 'katame.' Which ramen is your favorite?</t>
+          <t>This is the story of a small spacecraft called 'Hayabusa.' It took on the world's first mission to travel to a distant asteroid, collect rocks, and return. During the journey, its machines broke down again and again, and communication was lost. 'It's over,' many thought. But the researchers never gave up. After seven years and 6 billion kilometers, Hayabusa returned to Earth. At the end, it burned up itself while delivering only the capsule with the rocks. The whole world was moved to tears by that sight.</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>ぜひ 〜てみてください／〜によって／〜と 言いましょう</t>
+          <t>挑みました／あきらめませんでした／世界中が 涙した</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>紹介＋注文の実用。</t>
+          <t>困難→不屈→感動の帰還を聞く。</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>おいしそうで食欲がわく。</t>
+          <t>実話の感動＋宇宙ロマン＝記憶に残る。</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
+          <t>1話者・ナレーション(語り)</t>
         </is>
       </c>
     </row>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>カイのストーリー</t>
+          <t>カイの物語/日本生活スタート</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>カイのストーリー</t>
+          <t>カイの物語/日本生活スタート</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>カイのストーリー</t>
+          <t>カイの物語/日本一人旅</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>カイのストーリー</t>
+          <t>カイの物語/カイの日常</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>カイのストーリー</t>
+          <t>カイの物語/カイの休憩室</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>カイのストーリー</t>
+          <t>カイの物語/カイの日常</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>カイのストーリー</t>
+          <t>カイの物語/日本一人旅</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -2064,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2764,35 +2764,42 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>日本（にほん）に 着（つ）いた。空港（くうこう）は とても 大（おお）きい。入国（にゅうこく）の 列（れつ）は 長（なが）かったけれど、係（かか）りの 人（ひと）は やさしかった。「ようこそ」と 言（い）ってくれた。荷物（にもつ）を 受（う）け取（と）って、電車（でんしゃ）の 駅（えき）を さがす。さあ、新（あたら）しい 生活（せいかつ）の はじまりだ。</t>
+          <t>（ナレーション）長（なが）い フライトの あと、カイは ついに 日本（にほん）に 着（つ）いた。空港（くうこう）は 人（ひと）で いっぱいだ。
+審査官（しんさかん）：パスポートを お願（ねが）いします。日本（にほん）には 何（なん）の ために 来（き）ましたか。
+カイ：えっと、留学（りゅうがく）です。日本語（にほんご）の 学校（がっこう）に 通（かよ）うんです。
+審査官：どのくらい いますか。
+カイ：1年（ねん）の 予定（よてい）です。
+審査官：はい、どうぞ。日本での 生活（せいかつ）、がんばってください。
+カイ：ありがとうございます！
+（ナレーション）スタンプを もらって、カイは 大（おお）きく 息（いき）を ついた。「やっと 来た…。これから 新（あたら）しい 毎日（まいにち）が 始（はじ）まるんだ」。</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>I arrived in Japan. The airport is huge. The immigration line was long, but the staff were kind. They said 'Welcome.' I picked up my luggage and looked for the train station. Now, my new life begins.</t>
+          <t>(Narration) After the long flight, Kai finally arrived in Japan. The airport is packed. / Officer: Passport, please. What did you come to Japan for? / Kai: Um, to study. I'll attend a Japanese language school. / Officer: How long will you stay? / Kai: About a year. / Officer: All right, go ahead. Good luck with your life in Japan. / Kai: Thank you! / (Narration) After getting the stamp, Kai let out a big breath. 'I'm finally here... A new daily life starts now.'</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>〜に 着いた／〜けれど／はじまりだ</t>
+          <t>えっと／〜んです／がんばってください</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>到着〜移動の体験＋気持ち。</t>
+          <t>入国の会話＋心情。会話表現「えっと/〜んです/〜んだ」。</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>新生活スタート（カイ連載 第1話）。</t>
+          <t>新生活 第1話・ドキドキ。</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>多声TTS:ナレーター/審査官/カイ</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2826,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>はじめての一人暮らし</t>
+          <t>ゴミ出しでこまった</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2834,25 +2841,32 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>今日（きょう）から 一人暮（ひとりぐ）らしだ。部屋（へや）は 小（ちい）さいけれど、自分（じぶん）だけの 場所（ばしょ）だ。でも、困（こま）ったことが ある。ゴミの 出（だ）し方（かた）が わからない。となりの 人（ひと）に 聞（き）いたら、ていねいに 教（おし）えてくれた。日本（にほん）の 人は 親切（しんせつ）だなと 思（おも）った。</t>
+          <t>（ナレーション）引（ひ）っ越（こ）しの 次（つぎ）の 日（ひ）。カイは ゴミぶくろを 持（も）って、こまっていた。
+カイ：あれ？ ゴミは どこに 出（だ）せば いいんだろう…。
+（ナレーション）ちょうど、となりの 人（ひと）が 通（とお）りかかった。
+カイ：あの、すみません。ゴミの 出（だ）し方（かた）が わからなくて…。
+となりの人：ああ、燃（も）えるゴミは 月曜（げつよう）と 木曜（もくよう）ですよ。朝（あさ）8時（じ）までに、そこの 角（かど）に 出（だ）してね。
+カイ：そうなんですね！ ありがとうございます。助（たす）かりました。
+となりの人：困（こま）ったら いつでも 聞（き）いてね。
+（ナレーション）カイは ほっとした。「日本（にほん）の 人（ひと）は 親切（しんせつ）だなあ」。</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>92</v>
+        <v>208</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>From today I live alone. The room is small, but it's my own place. But there's a problem—I don't know how to sort the trash. When I asked my neighbor, they kindly explained. I thought, Japanese people are so kind.</t>
+          <t>(Narration) The day after moving. Kai stood there holding a trash bag, troubled. / Kai: Huh? Where am I supposed to put the trash...? / (Narration) Just then, a neighbor passed by. / Kai: Um, excuse me. I don't know how to sort the trash... / Neighbor: Ah, burnable trash is Monday and Thursday. Put it at that corner by 8 a.m. / Kai: Oh, I see! Thank you, that helps. / Neighbor: Ask me anytime you're stuck. / (Narration) Kai felt relieved. 'Japanese people are so kind.'</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>一人暮らし／〜けれど／教えてくれた</t>
+          <t>〜ばいいんだろう／そうなんですね／〜てね</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>生活立ち上げの戸惑いと人の温かさ。</t>
+          <t>近所での会話＋気づき。会話表現「あれ?/〜なんですね/〜てね」。</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -2862,7 +2876,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>多声TTS:ナレーター/カイ/近所の人</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2908,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -2904,35 +2918,44 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>連休（れんきゅう）に、はじめて 京都（きょうと）へ 行（い）った。古（ふる）い お寺（てら）が たくさん あって、とても 美（うつく）しかった。着物（きもの）を 着（き）て 歩（ある）いている 人も いた。お昼（ひる）に 食（た）べた 抹茶（まっちゃ）の アイスは、わすれられない 味（あじ）だった。また 行きたい。</t>
+          <t>（ナレーション）連休（れんきゅう）、カイは はじめて 一人（ひとり）で 京都（きょうと）へ 来た。古（ふる）い お寺（てら）が 美（うつく）しい。
+カイ：わあ、きれい…。あの、すみません、写真（しゃしん）を 撮（と）って もらえますか。
+通行人（つうこうにん）：いいですよ。はい、チーズ！
+カイ：ありがとうございます！
+（ナレーション）お昼（ひる）に、小（ちい）さな お店（みせ）に 入（はい）った。
+店員：いらっしゃい。何（なに）に しますか。
+カイ：抹茶（まっちゃ）の アイス、ください。
+店員：はいよ。京都（きょうと）は どう？
+カイ：最高（さいこう）です！ また 来（き）たいなあ。
+（ナレーション）わすれられない 一日（いちにち）に なった。</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>On the holidays, I went to Kyoto for the first time. There were many old temples, and they were very beautiful. Some people walked around in kimono. The matcha ice cream I had for lunch was an unforgettable taste. I want to go again.</t>
+          <t>(Narration) On the holidays, Kai came to Kyoto alone for the first time. The old temples are beautiful. / Kai: Wow, beautiful... Um, excuse me, could you take a photo? / Passerby: Sure. Okay, cheese! / Kai: Thank you! / (Narration) For lunch, he went into a small shop. / Clerk: Welcome. What'll you have? / Kai: Matcha ice cream, please. / Clerk: Coming up. How's Kyoto? / Kai: It's the best! I want to come again. / (Narration) It became an unforgettable day.</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>はじめて 〜へ 行った／〜も いた／また 行きたい</t>
+          <t>撮って もらえますか／また 来たいなあ／〜はどう?</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>旅行の描写＋感想。</t>
+          <t>旅先の会話。会話表現「わあ/はいよ/〜なあ」。</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>旅情・食・文化。</t>
+          <t>旅情・写真・食。</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>多声TTS:ナレーター/カイ/通行人/店員</t>
         </is>
       </c>
     </row>
@@ -2954,17 +2977,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/カイの日常</t>
+          <t>カイの物語/日本一人旅</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>はじめての美容院</t>
+          <t>お祭りに行く</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -2974,35 +2997,43 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>今日（きょう）は はじめて 一人（ひとり）で 美容院（びよういん）に 行（い）った。日本語（にほんご）で 髪型（かみがた）を 説明（せつめい）するのは ドキドキした。「少（すこ）し 短（みじか）く してください」と 言（い）ったら、思（おも）ったより ずいぶん 短く なって しまった。でも、美容師（びようし）さんが 「似合（にあ）っていますよ」と 言ってくれたので、うれしかった。次（つぎ）は もっと くわしく 伝（つた）えられるように なりたい。</t>
+          <t>（ナレーション）夏（なつ）の 夜（よる）。カイは 友（とも）だちの ミナと お祭（まつ）りに 来た。
+ミナ：カイ、ゆかた 似合（にあ）ってる！
+カイ：本当（ほんとう）？ えへへ、はじめて 着（き）たんだ。
+ミナ：屋台（やたい）、行（い）こうよ。たこ焼（や）き 食（た）べたい！
+カイ：いいね。あ、かき氷（ごおり）も！
+（ナレーション）二人（ふたり）が 食（た）べながら 歩（ある）いていると、空（そら）に 大（おお）きな 花火（はなび）が 上（あ）がった。
+カイ：わあ…！ きれいだね。
+ミナ：うん。来（き）て よかったね。
+（ナレーション）大（おお）きな 音（おと）と 光（ひかり）。カイの 胸（むね）は どきどきしていた。</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Today I went to a hair salon alone for the first time. Explaining my hairstyle in Japanese was nerve-racking. When I said 'a little shorter, please,' it came out much shorter than I expected. But the stylist said 'It suits you,' so I was happy. Next time I want to explain in more detail.</t>
+          <t>(Narration) A summer night. Kai came to a festival with his friend Mina. / Mina: Kai, the yukata looks good on you! / Kai: Really? Hehe, it's my first time wearing one. / Mina: Let's go to the stalls. I want takoyaki! / Kai: Nice. Oh, shaved ice too! / (Narration) As the two walked while eating, big fireworks rose into the sky. / Kai: Wow...! It's beautiful. / Mina: Yeah. I'm glad we came. / (Narration) The loud sound and light. Kai's heart was racing.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>はじめて 一人で／〜てしまった／似合っています</t>
+          <t>似合ってる／〜たんだ／来て よかったね</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>体験＋気持ちの流れ（日常）。</t>
+          <t>友だちとの祭り会話。会話表現「えへへ/〜よ/〜だね」。</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>カイの小さな成長。</t>
+          <t>夏祭りの高揚・友情。</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>多声TTS:ナレーター/カイ/ミナ</t>
         </is>
       </c>
     </row>
@@ -3024,17 +3055,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/カイの休憩室</t>
+          <t>カイの物語/カイの日常</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>カイのつぶやき：好きな食べ物</t>
+          <t>はじめての美容院</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -3044,35 +3075,44 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>ちょっと 休憩（きゅうけい）。みなさん、こんにちは、カイです。今日（きょう）は ぼくの 好（す）きな 食（た）べ物（もの）の 話（はなし）。実（じつ）は、ぼくは おにぎりが 大好（だいす）きです。コンビニの おにぎりも おいしいけれど、自分（じぶん）で 作（つく）るのも 楽（たの）しいです。みなさんの 好きな 日本（にほん）の 食べ物は 何（なん）ですか？</t>
+          <t>（ナレーション）カイは はじめて 一人（ひとり）で 美容院（びよういん）に 来た。日本語（にほんご）で 髪型（かみがた）を 言（い）うのは ドキドキする。
+美容師（びようし）：今日（きょう）は どうしますか。
+カイ：えっと、少（すこ）し 短（みじか）く して、軽（かる）く したいんです。
+美容師：前髪（まえがみ）は どうしましょう？
+カイ：前髪は そのままで お願（ねが）いします。
+（ナレーション）はさみの 音（おと）が ひびく。終（お）わって 鏡（かがみ）を 見（み）ると…思（おも）ったより ずいぶん 短（みじか）い！
+カイ：（心の声）うわ、短く なりすぎたかな…。
+美容師：うん、似合（にあ）っていますよ。
+カイ：あ、ありがとうございます！
+（ナレーション）少（すこ）し 短すぎたけれど、カイは なんだか うれしかった。</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>A little break. Hi everyone, it's Kai. Today, a chat about my favorite food. Actually, I love onigiri (rice balls). Convenience-store onigiri are tasty, but making them myself is fun too. What's your favorite Japanese food?</t>
+          <t>(Narration) Kai came to a hair salon alone for the first time. Saying his hairstyle in Japanese is nerve-racking. / Stylist: What would you like today? / Kai: Um, a bit shorter and lighter, please. / Stylist: What about your bangs? / Kai: Please leave the bangs as they are. / (Narration) The scissors snip away. When it was done and he looked in the mirror... it was much shorter than he expected! / Kai: (inner voice) Whoa, maybe too short... / Stylist: Yeah, it suits you. / Kai: Oh, thank you! / (Narration) A little too short, but Kai felt somehow happy.</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>ちょっと 休憩／実は／〜は 何ですか？</t>
+          <t>〜したいんです／どうしましょう／似合っています</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>カイの語りかけ・気軽な小ネタ（休憩室）。</t>
+          <t>美容院の会話＋心の声。会話表現「えっと/うわ/なんだか」。</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>親近感・問いかけ。</t>
+          <t>カイの小さな挑戦。</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>多声TTS:ナレーター/カイ/美容師</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3144,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3114,25 +3154,32 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>日本（にほん）に 来（き）て すぐは、友（とも）だちが いなくて さびしかった。でも、日本語（にほんご）の 教室（きょうしつ）で となりに 座（すわ）った 人（ひと）が、やさしく 話（はな）しかけて くれた。「いっしょに お昼（ひる）、食（た）べない？」その 一言（ひとこと）が とても うれしかった。今（いま）では、休（やす）みの 日（ひ）に いっしょに 出（で）かける 仲（なか）だ。勇気（ゆうき）を 出（だ）して よかった。</t>
+          <t>（ナレーション）日本（にほん）に 来（き）た ばかりの ころ、カイは 友（とも）だちが いなくて さびしかった。ある日（ひ）、日本語（にほんご）の 教室（きょうしつ）で…
+クラスメート：あ、その ペン、いいね。どこで 買（か）ったの？
+カイ：えっ、これ？ 駅前（えきまえ）の お店（みせ）です。
+クラスメート：へえ。ねえ、よかったら いっしょに お昼（ひる）、食（た）べない？
+カイ：いいんですか？ うれしいです！
+（ナレーション）その 一言（ひとこと）が、とても うれしかった。
+カイ：（心の声）勇気（ゆうき）を 出（だ）して よかった…！
+（ナレーション）今（いま）では、休（やす）みの 日（ひ）に いっしょに 出（で）かける 仲（なか）だ。</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>119</v>
+        <v>185</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Right after I came to Japan, I had no friends and felt lonely. But in Japanese class, the person who sat next to me kindly spoke to me: 'Want to have lunch together?' That one phrase made me so happy. Now we're close enough to go out on days off. I'm glad I found the courage.</t>
+          <t>(Narration) Just after coming to Japan, Kai had no friends and felt lonely. One day, in Japanese class... / Classmate: Oh, that pen's nice. Where'd you buy it? / Kai: Huh, this? At the shop in front of the station. / Classmate: Huh. Hey, if you'd like, want to have lunch together? / Kai: Really? I'd love to! / (Narration) That one phrase made him so happy. / Kai: (inner voice) I'm so glad I found the courage...! / (Narration) Now they're close enough to go out together on days off.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>さびしかった／話しかけて くれた／勇気を 出して よかった</t>
+          <t>どこで 買ったの？／いっしょに 〜ない？／よかったら</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>友だち作りの体験と気持ち（日常）。</t>
+          <t>友だち作りの会話。会話表現「えっ/へえ/ねえ」。誘いの「〜ない?」。</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3142,7 +3189,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>多声TTS:ナレーター/カイ/クラスメート</t>
         </is>
       </c>
     </row>
@@ -3164,17 +3211,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/日本一人旅</t>
+          <t>カイの物語/カイの休憩室</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>お祭りに行く</t>
+          <t>好きな食べ物の話</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>一人称</t>
+          <t>物語</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -3184,35 +3231,39 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>夏（なつ）の 夜（よる）、はじめて 日本（にほん）の お祭（まつ）りに 行（い）った。たくさんの 人（ひと）が ゆかたを 着（き）ていて、とても きれいだった。屋台（やたい）で たこ焼（や）きと かき氷（ごおり）を 買（か）って 食（た）べた。最後（さいご）に 花火（はなび）が 上（あ）がった。大（おお）きな 音（おと）と 光（ひかり）に、胸（むね）が どきどきした。日本の 夏（なつ）は、わすれられない 思（おも）い出（で）に なった。</t>
+          <t>カイ：みなさん、こんにちは、カイです。ちょっと 休憩（きゅうけい）の 時間（じかん）。今日（きょう）は ぼくの 好（す）きな 食（た）べ物（もの）の 話（はなし）。
+（ナレーション）実（じつ）は カイ、おにぎりが 大好物（だいこうぶつ）。
+カイ：コンビニの おにぎりも おいしいけど、自分（じぶん）で 作（つく）るのも 楽（たの）しいんだよね。この前（まえ）、友（とも）だちに 作（つく）ってあげたら「うまっ！」って 言（い）われて、うれしくて さ。
+（ナレーション）カイは 照（て）れながら 笑（わら）った。
+カイ：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>On a summer night, I went to a Japanese festival for the first time. Many people wore yukata and looked beautiful. At the stalls I bought and ate takoyaki and shaved ice. At the end, fireworks went up. The loud sound and light made my heart race. Japan's summer became an unforgettable memory.</t>
+          <t>Kai: Hi everyone, it's Kai. A little break time. Today, a talk about my favorite food. / (Narration) Actually, Kai loves onigiri. / Kai: Convenience-store onigiri are tasty, but making them yourself is fun too, you know. The other day I made some for a friend and they said 'Yum!'—it made me really happy. / (Narration) Kai laughed bashfully. / Kai: What's your favorite Japanese food? Let me know sometime. See you!</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>はじめて／〜を 買って 食べた／わすれられない 思い出</t>
+          <t>〜んだよね／うまっ／〜てね</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>お祭りの描写＋感動（旅行・季節）。</t>
+          <t>カイの語りかけ＋ひとり言。くだけた会話表現「〜だよね/うまっ/さ」。</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>夏祭りの高揚・五感で楽しい。</t>
+          <t>親近感・リスナーへの呼びかけ。</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1話者・カイ</t>
+          <t>多声TTS:カイ/ナレーター</t>
         </is>
       </c>
     </row>
@@ -3254,35 +3305,40 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が 流（なが）れて きました。おばあさんが 桃を 切（き）ると、中（なか）から 元気（げんき）な 男（おとこ）の子（こ）が 生（う）まれました。名前（なまえ）を 桃太郎（ももたろう）と つけました。桃太郎は 大（おお）きく なって、鬼（おに）を 退治（たいじ）しに 行くことに しました。</t>
+          <t>（ナレーション）むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が どんぶらこ、どんぶらこ、と 流（なが）れて きました。
+おばあさん：おや、なんて 大（おお）きな 桃（もも）だろう！ 家（いえ）に 持（も）って 帰（かえ）りましょう。
+（ナレーション）家（いえ）で 桃（もも）を 切（き）ろうとすると…パカッ！ 中（なか）から 元気（げんき）な 男（おとこ）の子（こ）が 生（う）まれました。
+おじいさん：おお、元気（げんき）な 子（こ）だ！ 名前（なまえ）は 桃太郎（ももたろう）に しよう。
+（ナレーション）大（おお）きく なった 桃太郎（ももたろう）は、ある日（ひ） 言（い）いました。
+桃太郎：おじいさん、おばあさん。鬼（おに）を 退治（たいじ）しに 行（い）ってきます！</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Long ago, in a certain place, lived an old man and an old woman. One day, a big peach came floating down the river. When the old woman cut it open, a healthy boy was born from inside. They named him Momotaro. Momotaro grew up and decided to go defeat the ogres.</t>
+          <t>(Narration) Long ago, an old man and an old woman lived in a certain place. One day, a big peach came floating down the river, donburako, donburako. / Old woman: Oh my, what a big peach! Let's take it home. / (Narration) When they tried to cut the peach at home... crack! A healthy boy was born from inside. / Old man: Oh, a lively boy! Let's name him Momotaro. / (Narration) When Momotaro grew up, one day he said: / Momotaro: Grandpa, Grandma. I'm going off to defeat the ogres!</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>むかしむかし／〜と いいました／〜ことに した</t>
+          <t>なんて 〜だろう／〜ましょう／〜てきます</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>昔話の定型表現に親しむ。</t>
+          <t>昔話の会話＋擬音(どんぶらこ/パカッ)。</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>有名な物語で親しみやすい。</t>
+          <t>有名な昔話を会話で。</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1話者・語り</t>
+          <t>多声TTS:ナレーター/おばあさん/おじいさん/桃太郎</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3360,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>日本語ミステリー</t>
+          <t>ミステリー</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -3324,35 +3380,40 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。朝（あさ）、店（みせ）を 開（あ）けると、一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が 10個（こ）、消（き）えていたのだ。店長（てんちょう）は あわてて 駅員（えきいん）の 田中（たなか）さんに 相談（そうだん）した。「鍵（かぎ）は かかっていたのに、どうして…？」田中さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
+          <t>（ナレーション）東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。
+店長（てんちょう）：たいへんだ！ 一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が、10個（こ）も 消（き）えてる！
+駅員（えきいん）の田中（たなか）：鍵（かぎ）は かかっていたんですよね？
+店長：はい、朝（あさ）まで しっかり…。
+田中：おかしいな。鍵（かぎ）が かかっていたのに、どうやって…？
+（ナレーション）田中（たなか）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>An incident occurred at a famous ekiben (station bento) shop in Tokyo Station. In the morning, when they opened, 10 of the most popular 'Sea Bounty Bento' had vanished. The flustered manager consulted station attendant Tanaka. 'The door was locked, so how...?' Tanaka thought. This might not be an ordinary thief.</t>
+          <t>(Narration) An incident occurred at a famous ekiben shop in Tokyo Station. / Manager: This is terrible! Ten of our most popular 'Sea Bounty Bento' have vanished! / Tanaka (staff): The door was locked, right? / Manager: Yes, firmly until morning... / Tanaka: Strange. The door was locked, so how...? / (Narration) Tanaka thought. This might not be an ordinary thief.</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>事件が 起きた／消えていた／〜かもしれない</t>
+          <t>たいへんだ／〜んですよね／どうやって…?</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>事件の発端を読む（密室の謎）。</t>
+          <t>事件の発端を会話で（密室の謎）。</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>鍵がかかっていたのに消えた＝続きが気になる第1話。</t>
+          <t>続きが気になる第1話。</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1話者・語り(緊張感)</t>
+          <t>多声TTS:ナレーター/店長/田中</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3435,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>日本語ミステリー</t>
+          <t>ミステリー</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3394,35 +3455,41 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>田中（たなか）さんは、店（みせ）の 近（ちか）くに いた 人（ひと）たちに 話（はなし）を 聞（き）いた。掃除（そうじ）の おばさん：「朝（あさ）5時（じ）ごろ、白（しろ）い 服（ふく）の 人を 見（み）ました」。となりの コーヒー店（てん）の 店員（てんいん）：「変（へん）な 音（おと）が しました」。でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。田中さんは 首（くび）を かしげた。「おかしいな…」</t>
+          <t>田中（たなか）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
+掃除（そうじ）の人：5時（じ）ごろ、白（しろ）い 服（ふく）の 人（ひと）を 見（み）ましたよ。
+田中：白い 服…。ありがとうございます。
+コーヒー店（てん）の人：そういえば、変（へん）な 音（おと）が しましたね。バサバサっと。
+田中：バサバサ？
+（ナレーション）でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。
+田中：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Tanaka asked people who had been near the shop. Cleaning lady: 'Around 5 a.m., I saw someone in white clothes.' The neighboring coffee-shop clerk: 'There was a strange sound.' But the security camera showed no one. Tanaka tilted his head. 'Strange...'</t>
+          <t>Tanaka: Excuse me, did you see anything this morning? / Cleaner: Around 5, I saw someone in white clothes. / Tanaka: White clothes... Thank you. / Coffee-shop worker: Come to think of it, there was a strange sound. A flapping sound. / Tanaka: Flapping? / (Narration) But the security camera showed no one. / Tanaka: (tilting his head) Hmm, that's strange...</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>話を 聞いた／〜を 見ました／だれも 映っていない</t>
+          <t>見ませんでしたか／そういえば／うーん</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>証言の聞き取りと矛盾を読む。</t>
+          <t>証言の会話と矛盾。会話表現「そういえば/うーん」。</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>目撃者はいるのにカメラに映らない＝謎が深まる。</t>
+          <t>謎が深まる。</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:刑事/証人たち</t>
+          <t>多声TTS:田中/証人たち/ナレーター</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3511,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>日本語ミステリー</t>
+          <t>ミステリー</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -3464,35 +3531,40 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>次（つぎ）の 日（ひ）、田中（たなか）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。男は 駅（えき）の 清掃員（せいそういん）だった。「あの 朝（あさ）、何（なに）を していましたか」。男：「私（わたし）は ただ、ゴミを 集（あつ）めていただけです」。でも、男の カバンから、弁当（べんとう）の 包（つつ）み紙（がみ）が 落（お）ちた。田中さんの 目（め）が 光（ひか）った。「これは…？」</t>
+          <t>（ナレーション）次（つぎ）の 日（ひ）、田中（たなか）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。駅（えき）の 清掃員（せいそういん）だ。
+田中：あの 朝（あさ）、何（なに）を していましたか。
+清掃員：私（わたし）は ただ、ゴミを 集（あつ）めていただけですよ。
+（ナレーション）そのとき、男（おとこ）の カバンから 弁当（べんとう）の 包（つつ）み紙（がみ）が ひらり、と 落（お）ちた。
+田中：（目（め）を 光（ひか）らせて）…これは？
+清掃員：えっ、いや、これは…！</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>The next day, Tanaka found the man in white—a station cleaner. 'What were you doing that morning?' Man: 'I was just collecting trash.' But a bento wrapper fell from his bag. Tanaka's eyes flashed. 'What's this...?'</t>
+          <t>(Narration) The next day, Tanaka found the man in white—a station cleaner. / Tanaka: What were you doing that morning? / Cleaner: I was just collecting trash. / (Narration) Just then, a bento wrapper fluttered out of the man's bag. / Tanaka: (eyes flashing) ...What's this? / Cleaner: Huh, no, this is...!</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>容疑者／〜ていただけです／目が 光った</t>
+          <t>〜だけですよ／これは？／えっ、いや</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>容疑者への質問と証拠を読む。</t>
+          <t>容疑者への会話と証拠。会話表現「〜だけですよ/えっ、いや」。</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>決定的証拠?＝犯人かの緊張。</t>
+          <t>犯人か?の緊張。</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:刑事/容疑者</t>
+          <t>多声TTS:ナレーター/田中/清掃員</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3586,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>日本語ミステリー</t>
+          <t>ミステリー</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3534,35 +3606,40 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>田中（たなか）さんは 包（つつ）み紙（がみ）を よく 見（み）た。男（おとこ）：「それは 私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！」実（じつ）は、犯人（はんにん）は 人（ひと）では なかった。防犯（ぼうはん）カメラを もう一度（いちど）見（み）ると、屋根（やね）の すきまから、大（おお）きな カラスが 弁当（べんとう）を 運（はこ）んでいた！みんな 大笑（おおわら）い。「鍵（かぎ）の 謎（なぞ）は、小（ちい）さな 窓（まど）だったのか」。事件（じけん）は 無事（ぶじ）解決（かいけつ）した。</t>
+          <t>清掃員：それは、私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！
+（ナレーション）田中（たなか）さんは 防犯（ぼうはん）カメラを もう一度（いちど）見（み）た。すると、屋根（やね）の すきまから…
+田中：あっ！ 見（み）て ください。大（おお）きな カラスが、弁当（べんとう）を 運（はこ）んでる！
+店長：えーっ！ 犯人（はんにん）は カラス だったの！？
+（ナレーション）みんな 大笑（おおわら）い。鍵（かぎ）の 謎（なぞ）は、屋根（やね）の 小（ちい）さな 窓（まど）だったのだ。
+田中：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Tanaka looked closely at the wrapper. Man: 'That's trash I picked up. It's true!' In fact, the culprit wasn't a person. Watching the camera again—through a gap in the roof, a big crow was carrying the bento! Everyone burst out laughing. 'So the locked-room mystery was a small window.' The case was happily solved.</t>
+          <t>Cleaner: That's trash I picked up. It's true! / (Narration) Tanaka watched the security camera again. Then, through a gap in the roof... / Tanaka: Ah! Look! A big crow is carrying the bento! / Manager: Whaaat! The culprit was a crow?! / (Narration) Everyone burst out laughing. The mystery of the lock was a small window in the roof. / Tanaka: Haha, case closed.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>よく 見た／実は／無事 解決した</t>
+          <t>見て ください／〜だったの!?／無事 解決</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>真相・どんでん返しを読む。</t>
+          <t>真相を会話で。会話表現「あっ/えーっ/はは」。</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>犯人はカラス＝意外な落ちでスッキリ。</t>
+          <t>犯人はカラス＝意外な落ち。</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:刑事/容疑者</t>
+          <t>多声TTS:ナレーター/田中/清掃員/店長</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3661,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>怖い話</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>真夜中の水の音</t>
+          <t>カップラーメンの誕生</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3604,35 +3681,42 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>夜中（よなか）、トイレに 起（お）きた。家（いえ）には 私（わたし）一人（ひとり）の はずだった。でも、台所（だいどころ）から 水（みず）の 音（おと）が 聞（き）こえる。だれかが 蛇口（じゃぐち）を 使（つか）っている…？こわごわ のぞくと、誰（だれ）も いない。ただ、コップに 水が いっぱい 入（はい）っていた。私（わたし）は 飲（の）んでいない。あの 水は、だれが…。</t>
+          <t>（ナレーション）戦後（せんご）の 日本（にほん）。町（まち）には 食（た）べ物（もの）を 求（もと）める 人々（ひとびと）の 長（なが）い 行列（ぎょうれつ）が あった。それを 見（み）て、一人（ひとり）の 男（おとこ）、安藤（あんどう）さんは 強（つよ）く 思（おも）った。
+安藤：お湯（ゆ）を 入（い）れるだけで すぐ 食（た）べられる めんが あれば、みんなが 助（たす）かるはずだ。
+（ナレーション）その日（ひ）から、小（ちい）さな 小屋（こや）に こもる 毎日（まいにち）が 始（はじ）まった。
+妻（つま）：あなた、また 徹夜（てつや）ですか。体（からだ）を こわしますよ。
+安藤：あと 少（すこ）しなんだ。あきらめるわけには いかない。
+（ナレーション）失敗（しっぱい）は 数（かぞ）えきれない。めんが すぐ 悪（わる）くなって しまう。ある日（ひ）、妻（つま）が 作（つく）る 天（てん）ぷらを 見（み）て——
+安藤：そうか！ 油（あぶら）で あげれば、水分（すいぶん）が とんで、めんが かわく！
+（ナレーション）こうして、世界（せかい）で はじめての インスタントラーメンが 生（う）まれた。今（いま）では 世界中（せかいじゅう）で 一年（いちねん）に 1000億（おく）食（しょく）。小（ちい）さな ひらめきが、本当（ほんとう）に 世界（せかい）を 変（か）えたのだ。</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>107</v>
+        <v>293</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>In the middle of the night, I got up for the toilet. I should have been alone in the house. But I heard the sound of water from the kitchen. Was someone using the faucet...? Fearfully I peeked in—no one. Just a glass full of water. I hadn't poured it. Who filled that glass...?</t>
+          <t>(Narration) Postwar Japan. In the towns were long lines of people seeking food. Seeing that, one man, Mr. Ando, thought strongly: / Ando: If there were noodles you could eat right away just by adding hot water, it would help everyone. / (Narration) From that day, days of shutting himself in a small shed began. / Wife: Dear, an all-nighter again? You'll ruin your health. / Ando: Just a little more. I can't give up. / (Narration) The failures were countless—the noodles spoiled quickly. One day, watching his wife make tempura— / Ando: That's it! If you fry them in oil, the water evaporates and the noodles dry! / (Narration) Thus the world's first instant ramen was born. Today, 100 billion servings a year worldwide. A small spark truly changed the world.</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>〜のはず／聞こえる／だれも いない</t>
+          <t>〜はずだ／あきらめるわけには いかない／そうか！</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>怪談の“間”と落ちを味わう。</t>
+          <t>困難→不屈→ひらめき→成功。会話で臨場感。</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>ゾクッとする中毒性。</t>
+          <t>身近なカップ麺の感動秘話・濃い内容。</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1話者・低めの声</t>
+          <t>多声TTS:ナレーター/安藤/妻</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3743,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>カップラーメンの誕生</t>
+          <t>はやぶさの帰還</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3674,109 +3758,41 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>戦後（せんご）の 日本（にほん）。食（た）べ物（もの）が 少（すく）なく、人々（ひとびと）は 困（こま）っていた。一人（ひとり）の 男（おとこ）、安藤（あんどう）さんは 考（かんが）えた。「お湯（ゆ）を 入（い）れるだけで 食べられる めんを 作（つく）れないか」。
-毎日（まいにち）、朝（あさ）から 夜（よる）まで 研究（けんきゅう）した。何度（なんど）も 失敗（しっぱい）した。でも、あきらめなかった。ある日（ひ）、妻（つま）が 作る 天（てん）ぷらを 見（み）て、ひらめいた。「油（あぶら）で あげれば、めんが かわく！」
-こうして、世界（せかい）で はじめての インスタントラーメンが 生（う）まれた。今（いま）では、世界中（せかいじゅう）で 一年（いちねん）に 1000億（おく）食（しょく）も 食べられている。小（ちい）さな ひらめきが、世界を 変（か）えたのだ。</t>
+          <t>（ナレーション）小（ちい）さな 宇宙船（うちゅうせん）「はやぶさ」は、地球（ちきゅう）から 3億（おく）キロ 離（はな）れた 小惑星（しょうわくせい）を 目指（めざ）した。星（ほし）の 石（いし）を 取（と）って 帰（かえ）る——だれも 成功（せいこう）した ことの ない 挑戦（ちょうせん）だった。
+（ナレーション）しかし、旅（たび）は 苦難（くなん）の 連続（れんぞく）。エンジンは こわれ、ついに 通信（つうしん）も 切（き）れた。
+研究者（けんきゅうしゃ）A：信号（しんごう）が…ありません。はやぶさが、いません。
+研究者B：あきらめるな。きっと どこかで 生（い）きている。呼（よ）び続（つづ）けよう。
+（ナレーション）管制室（かんせいしつ）の 人々（ひとびと）は、来（く）る日（ひ）も 来る日も 信号（しんごう）を 送（おく）り続（つづ）けた。そして 7週間後（しゅうかんご）——
+研究者A：…返事（へんじ）が、来（き）ました！ はやぶさ、生（い）きてます！
+（ナレーション）7年（ねん）、60億（おく）キロの 旅（たび）の すえ、はやぶさは 帰（かえ）ってきた。最後（さいご）は 自分（じぶん）の 体（からだ）を 燃（も）やしながら、石（いし）の カプセルだけを そっと 送（おく）り届（とど）けた。その 光（ひかり）に、世界中（せかいじゅう）が 涙（なみだ）した。</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>206</v>
+        <v>283</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Postwar Japan. Food was scarce and people were struggling. One man, Mr. Ando, thought: 'Couldn't I make noodles you can eat just by adding hot water?' Every day, from morning to night, he researched. He failed many times. But he never gave up. One day, watching his wife make tempura, it hit him: 'If you fry them in oil, the noodles dry out!' Thus the world's first instant ramen was born. Today, 100 billion servings are eaten worldwide each year. A small spark of insight changed the world.</t>
+          <t>(Narration) The small spacecraft 'Hayabusa' aimed for an asteroid 300 million km from Earth. To collect rocks from a star and return—a challenge no one had ever succeeded at. / (Narration) But the journey was one hardship after another. The engines broke, and finally communication was lost. / Researcher A: There's... no signal. Hayabusa is gone. / Researcher B: Don't give up. It's surely alive somewhere. Let's keep calling. / (Narration) The control room kept sending signals day after day. Then, seven weeks later— / Researcher A: ...A reply came! Hayabusa is alive! / (Narration) After seven years and 6 billion km, Hayabusa came home. At the end, burning up its own body, it gently delivered only the capsule of rocks. The whole world wept at that light.</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>あきらめなかった／ひらめいた／世界を 変えた</t>
+          <t>あきらめるな／返事が 来ました／〜のすえ</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>困難→挑戦→転機→成功 の物語の流れを聞く。</t>
+          <t>苦難→不屈→奇跡の帰還。管制室の会話で手に汗。</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>身近なカップ麺の“感動の誕生秘話”＝あこがれ・記憶に残る。</t>
+          <t>実話の大感動・濃い内容。</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1話者・ナレーション(語り)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>L-023</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>はやぶさの帰還</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>「はやぶさ」という 小（ちい）さな 宇宙船（うちゅうせん）の 話（はなし）です。はやぶさは、地球（ちきゅう）から 遠（とお）い 小惑星（しょうわくせい）まで 行（い）き、石（いし）を 取（と）って 帰（かえ）る という 世界（せかい）で はじめての ミッションに 挑（いど）みました。
-旅（たび）の 途中（とちゅう）、機械（きかい）が 何度（なんど）も こわれ、通信（つうしん）も 切（き）れました。「もう だめか」と 多（おお）くの 人（ひと）が 思（おも）いました。でも、研究者（けんきゅうしゃ）たちは あきらめませんでした。
-7年（ねん）、60億（おく）キロの 旅（たび）の すえ、はやぶさは 地球に 戻（もど）りました。最後（さいご）は 自分（じぶん）は 燃（も）えながら、石（いし）の 入（はい）った カプセルだけを 送（おく）り届（とど）けたのです。その 姿（すがた）に、世界中（せかいじゅう）が 涙（なみだ）しました。</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>209</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>This is the story of a small spacecraft called 'Hayabusa.' It took on the world's first mission to travel to a distant asteroid, collect rocks, and return. During the journey, its machines broke down again and again, and communication was lost. 'It's over,' many thought. But the researchers never gave up. After seven years and 6 billion kilometers, Hayabusa returned to Earth. At the end, it burned up itself while delivering only the capsule with the rocks. The whole world was moved to tears by that sight.</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>挑みました／あきらめませんでした／世界中が 涙した</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>困難→不屈→感動の帰還を聞く。</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>実話の感動＋宇宙ロマン＝記憶に残る。</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>1話者・ナレーション(語り)</t>
+          <t>多声TTS:ナレーター/研究者A/研究者B</t>
         </is>
       </c>
     </row>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>使えるひとこと</t>
+          <t>使える一言</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>使えるひとこと</t>
+          <t>使える一言</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>使えるひとこと</t>
+          <t>使える一言</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ことば遊び</t>
+          <t>言葉遊び</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>ことば遊び</t>
+          <t>言葉遊び</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ことば遊び</t>
+          <t>言葉遊び</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1856,14 +1856,10 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
           <t>本音講座</t>
         </is>
       </c>
+      <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>「大丈夫です」の正体</t>
@@ -1926,14 +1922,10 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>あるある</t>
-        </is>
-      </c>
+          <t>日本と世界の違い</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>日本の電車は静か</t>
@@ -1996,14 +1988,10 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>文化と本音</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>食べもの</t>
-        </is>
-      </c>
+          <t>グルメ</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>ラーメンを食べよう</t>
@@ -2048,6 +2036,72 @@
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>S-020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>文化</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>お花見の楽しみ方</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の 春（はる）の 楽（たの）しみと いえば、お花見（はなみ）です。桜（さくら）が 咲（さ）くと、人々（ひとびと）は 公園（こうえん）に 集（あつ）まり、木（き）の 下（した）で お弁当（べんとう）を 食（た）べたり、おしゃべりを したり します。夜（よる）の 桜「夜桜（よざくら）」も きれいです。桜は 一週間（いっしゅうかん）ほどで 散（ち）って しまうので、その 短（みじか）い 美（うつく）しさを みんなで 楽（たの）しみます。</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Speaking of spring fun in Japan, it's hanami (cherry-blossom viewing). When the cherry trees bloom, people gather in parks, eating bento and chatting under the trees. The blossoms at night, 'yozakura,' are beautiful too. The blossoms scatter in about a week, so everyone enjoys that brief beauty together.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>〜と いえば／〜たり 〜たり／散ってしまう</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>お花見の文化。</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>日本の春の風物詩。</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>
@@ -2739,12 +2793,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>カイの物語</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/日本生活スタート</t>
+          <t>日本生活スタート</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2816,12 +2870,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>カイの物語</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/日本生活スタート</t>
+          <t>日本生活スタート</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2893,12 +2947,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>カイの物語</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/日本一人旅</t>
+          <t>日本一人旅</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2972,12 +3026,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>カイの物語</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/日本一人旅</t>
+          <t>日本一人旅</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3050,12 +3104,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>カイの物語</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/カイの日常</t>
+          <t>カイの日常</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -3129,12 +3183,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>カイの物語</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/カイの日常</t>
+          <t>カイの日常</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3206,12 +3260,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
+          <t>カイの物語</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>カイの物語/カイの休憩室</t>
+          <t>カイの休憩室</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -3280,14 +3334,10 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
           <t>昔話</t>
         </is>
       </c>
+      <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>桃太郎</t>
@@ -3355,14 +3405,10 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
           <t>ミステリー</t>
         </is>
       </c>
+      <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第1話：駅で事件発生</t>
@@ -3430,14 +3476,10 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
           <t>ミステリー</t>
         </is>
       </c>
+      <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第2話：証言を聞く</t>
@@ -3506,14 +3548,10 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
           <t>ミステリー</t>
         </is>
       </c>
+      <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第3話：容疑者登場</t>
@@ -3581,14 +3619,10 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
           <t>ミステリー</t>
         </is>
       </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第4話：真犯人は？</t>
@@ -3656,14 +3690,10 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
+      <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>カップラーメンの誕生</t>
@@ -3733,14 +3763,10 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
+      <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>はやぶさの帰還</t>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2107,6 +2107,1359 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>S-021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>文化</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>温泉に入る前に</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の 温泉（おんせん）には、楽（たの）しむための ルールが あります。まず、湯（ゆ）に 入（はい）る 前（まえ）に、体（からだ）を きれいに 洗（あら）います。そして、タオルは 湯（ゆ）の 中（なか）に 入（い）れません。頭（あたま）の 上（うえ）に のせる 人（ひと）も います。大（おお）きな 声（こえ）で さわがず、ゆっくり 温（あたた）まりましょう。マナーを 守（まも）れば、誰（だれ）でも 気持（きも）ちよく 過（す）ごせます。</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Japanese hot springs have rules for everyone's enjoyment. First, wash your body well before getting in. Don't put your towel in the water; some people rest it on their head. Don't be loud—relax and warm up slowly. If you follow the manners, everyone can have a pleasant time.</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>〜てから／〜ません／〜ば</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>温泉の基本マナー。</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>知らないと恥ずかしい温泉作法。</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>S-022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>文化</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>お正月の過ごし方</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の お正月（しょうがつ）は、一年（いちねん）で いちばん 大切（たいせつ）な 行事（ぎょうじ）です。大（おお）みそかの 夜（よる）には「年越（としこ）しそば」を 食（た）べ、元日（がんじつ）には 神社（じんじゃ）へ「初詣（はつもうで）」に 行（い）きます。家族（かぞく）で「おせち料理（りょうり）」を 食（た）べ、子（こ）どもは「お年玉（としだま）」を もらって 喜（よろこ）びます。『あけまして おめでとうございます』と あいさつを して、新（あたら）しい 年（とし）を 祝（いわ）います。</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>New Year is the most important event of the year in Japan. On New Year's Eve people eat 'toshikoshi soba,' and on New Year's Day they visit a shrine for 'hatsumode.' Families eat 'osechi' dishes, and children are delighted to receive 'otoshidama' (money gifts). People greet each other with 'Happy New Year' and celebrate the new year.</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>〜には／初詣／あけまして おめでとうございます</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>正月の主な習慣。</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>お年玉やおせちにわくわく。</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>S-023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>文化</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>「いただきます」の心</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>日本人（にほんじん）は 食事（しょくじ）の 前（まえ）に『いただきます』、後（あと）に『ごちそうさまでした』と 言（い）います。これは ただの あいさつでは ありません。野菜（やさい）や 肉（にく）など、食（た）べ物（もの）の「命（いのち）」と、料理（りょうり）を 作（つく）ってくれた 人（ひと）への 感謝（かんしゃ）の 言葉（ことば）です。だから、たとえ 一人（ひとり）で 食（た）べる ときでも、小（ちい）さな 声（こえ）で 言（い）う 人（ひと）が 多（おお）いのです。</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Before eating, Japanese people say 'itadakimasu,' and after, 'gochisosama deshita.' These aren't just greetings. They are words of gratitude for the 'life' of the food—vegetables, meat—and for the person who cooked it. That's why many people say them quietly even when eating alone.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>ただの〜では ない／〜てくれた／たとえ〜ても</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>食前後のあいさつの意味。</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>知ると食事が少し豊かに。</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>S-024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>文化</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>花火大会の夜</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>夏（なつ）の 日本（にほん）と いえば、花火大会（はなびたいかい）です。人々（ひとびと）は「浴衣（ゆかた）」を 着（き）て、屋台（やたい）で やきそばや かき氷（ごおり）を 買（か）います。空（そら）に 大（おお）きな 花火（はなび）が 上（あ）がると、みんな『たまや〜！』と 声（こえ）を あげます。ドンという 音（おと）と、夜空（よぞら）に 広（ひろ）がる 光（ひかり）は、夏（なつ）の いちばんの 思（おも）い出（で）に なります。</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Speaking of summer in Japan, it's fireworks festivals. People wear 'yukata' and buy yakisoba and shaved ice from food stalls. When big fireworks rise into the sky, everyone shouts 'Tamaya!' The booming sound and the light spreading across the night sky become the best memory of summer.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>〜と いえば／〜を 着て／〜が 上がる</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>夏祭り・花火の風景。</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>浴衣と屋台で気分が上がる。</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>S-025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>本音講座</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>「行けたら行く」の意味</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>友（とも）だちを 誘（さそ）った とき、『行（い）けたら 行（い）くね』と 言（い）われたら、どう 思（おも）いますか。実（じつ）は これ、多（おお）くの 場合（ばあい）「たぶん 行（い）かない」という 意味（いみ）です。日本人（にほんじん）は、はっきり「行（い）かない」と 言（い）うと 相手（あいて）を がっかりさせる と 考（かんが）えます。だから、やわらかい 断（ことわ）り方（かた）として よく 使（つか）われます。本気（ほんき）の ときは『絶対（ぜったい）行（い）く！』と 言（い）いますよ。</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>When you invite a friend and they say 'I'll come if I can,' what do you think? Actually, this often means 'probably not.' Japanese people feel that clearly saying 'I won't come' disappoints the other person, so it's used as a gentle refusal. When they really mean it, they'll say 'I'm definitely coming!'</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>〜たら／〜という 意味／断り方</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>やわらかい社交辞令。</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>言われてモヤッとする日本語No.1。</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>S-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>本音講座</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>「検討します」の正体</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>仕事（しごと）の 場面（ばめん）で『検討（けんとう）します』『前向（まえむ）きに 考（かんが）えます』と 言（い）われたら、注意（ちゅうい）が 必要（ひつよう）です。本当（ほんとう）に 考（かんが）える ことも ありますが、やんわりと「今回（こんかい）は むずかしい」と 伝（つた）えている ことも 多（おお）いのです。日本（にほん）の ビジネスでは、はっきり 断（ことわ）らずに 相手（あいて）の メンツを 守（まも）る 言（い）い方（かた）が 好（この）まれます。</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>In business, be careful if you hear 'We'll consider it' or 'We'll think about it positively.' Sometimes they really will, but often it gently means 'this time is difficult.' In Japanese business, ways of speaking that protect the other person's face without refusing outright are preferred.</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>検討します／やんわり／〜ことも 多い</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>ビジネスの建前。</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Yesに聞こえてNoかも。</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>S-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>本音講座</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ほめられた時の返事</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>田中（たなか）：日本語（にほんご）、お上手（じょうず）ですね！
+カイ：いいえ、まだまだです。
+田中：そんな ことないですよ。発音（はつおん）も きれいだし。
+カイ：ありがとうございます。でも、もっと 勉強（べんきょう）しないと。
+——日本（にほん）では、ほめられた とき すぐに「ありがとう」と 受（う）け取（と）るより、『いいえ、まだまだです』と 謙遜（けんそん）する ことが 多（おお）いです。</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Tanaka: Your Japanese is so good! / Kai: No, I still have a long way to go. / Tanaka: That's not true—your pronunciation is clear too. / Kai: Thank you. But I need to study more. — In Japan, rather than immediately accepting praise with 'thank you,' people often respond modestly with 'No, not yet.'</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>まだまだです／そんな ことない／謙遜</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>謙遜の受け答え。</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>ほめ言葉の正しい返し方。</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:2名</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>S-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>本音講座</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>「すみません」の七変化</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>『すみません』は、日本語（にほんご）で いちばん 便利（べんり）な 言葉（ことば）かもしれません。あやまる とき(=ごめんなさい)、お礼（れい）を 言（い）う とき(=ありがとう)、人（ひと）を 呼（よ）ぶ とき(=ちょっと いいですか)、どれにも 使（つか）えます。たとえば 電車（でんしゃ）で 席（せき）を ゆずって もらったら『すみません』。これは「ありがとう」の 意味（いみ）です。場面（ばめん）で 意味（いみ）が 変（か）わる、ふしぎな 言葉（ことば）です。</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>'Sumimasen' may be the most useful word in Japanese. You can use it to apologize (sorry), to thank (thank you), and to get attention (excuse me). For example, if someone gives up their seat for you on the train, you say 'sumimasen'—here it means 'thank you.' It's a curious word whose meaning changes with the situation.</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>すみません／〜たら／場面で 変わる</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>万能語すみません。</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>1語で3役の最強ワード。</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>S-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>日本と世界の違い</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>チップがない国</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>海外（かいがい）の レストランでは、料理（りょうり）の 代金（だいきん）の ほかに「チップ」を 払（はら）う 国（くに）が 多（おお）いです。でも、日本（にほん）には チップの 習慣（しゅうかん）が ありません。サービス料（りょう）は、最初（さいしょ）から 値段（ねだん）に 入（はい）っています。お店（みせ）の 人（ひと）は、チップを もらわなくても、とても ていねいに サービスして くれます。むしろ チップを 渡（わた）すと、相手（あいて）が 困（こま）って しまう ことも あります。</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>In restaurants abroad, many countries pay a 'tip' on top of the bill. But Japan has no tipping custom. The service charge is included in the price from the start. Staff serve very politely even without a tip. In fact, offering a tip can sometimes confuse them.</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>〜の ほかに／〜が ない／むしろ</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>チップ文化なし。</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>渡すと逆に困らせる!?</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>S-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>日本と世界の違い</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>玄関で靴を脱ぐ</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の 家（いえ）に 入（はい）る とき、必（かなら）ず 玄関（げんかん）で 靴（くつ）を 脱（ぬ）ぎます。これは、外（そと）の よごれを 家（いえ）の 中（なか）に 入（い）れない ためです。脱（ぬ）いだ 靴（くつ）は、つま先（さき）を 外（そと）の ほうへ 向（む）けて そろえると、きれいに 見（み）えます。学校（がっこう）や 病院（びょういん）、和室（わしつ）の お店（みせ）でも 靴（くつ）を 脱（ぬ）ぐ ことが あります。スリッパに はきかえる ことも 多（おお）いです。</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>When entering a home in Japan, you always take off your shoes at the entrance. This is to keep outside dirt out of the house. If you line up your shoes with the toes pointing outward, it looks neat. Schools, hospitals, and tatami-room restaurants may also require removing shoes, and often you change into slippers.</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>〜とき／〜ために／〜と …に 見える</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>靴を脱ぐ文化。</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>靴の向きまで気を配る。</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>S-031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>日本と世界の違い</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>まだ多い現金文化</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>世界（せかい）では カードや スマホ決済（けっさい）が 進（すす）んでいますが、日本（にほん）は 今（いま）でも「現金（げんきん）」を よく 使（つか）います。小（ちい）さな お店（みせ）や 古（ふる）い 食堂（しょくどう）では、カードが 使（つか）えない ことも あります。だから、少（すこ）し 現金（げんきん）を 持（も）って 歩（ある）くと 安心（あんしん）です。最近（さいきん）は キャッシュレスも 増（ふ）えて きましたが、地域（ちいき）に よって 差（さ）が あります。</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>While the world moves toward cards and smartphone payments, Japan still uses cash a lot. Small shops and old eateries sometimes don't accept cards. So it's reassuring to carry a little cash. Cashless payment has been increasing recently, but it varies by region.</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>〜でも／〜ことも ある／〜によって</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>現金がまだ強い。</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>カード不可の店に注意。</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>S-032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>日本と世界の違い</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>きれいに並ぶ国</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>駅（えき）や バス停（てい）、お店（みせ）の レジで、日本人（にほんじん）は 自然（しぜん）に 一列（いちれつ）に 並（なら）びます。電車（でんしゃ）を 待（ま）つ ときも、床（ゆか）の 印（しるし）に 沿（そ）って きれいに 並（なら）びます。割（わ）り込（こ）む 人（ひと）は ほとんど いません。みんなが 順番（じゅんばん）を 守（まも）るので、混（こ）んでいても 意外（いがい）と スムーズです。この「並（なら）ぶ 文化（ぶんか）」に 驚（おどろ）く 外国人（がいこくじん）も 多（おお）いです。</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>At stations, bus stops, and store registers, Japanese people naturally line up in a single file. Even when waiting for a train, they line up neatly along the marks on the floor. Almost no one cuts in. Because everyone keeps their turn, it's surprisingly smooth even when crowded. Many foreigners are amazed by this 'queuing culture.'</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>自然に／〜に 沿って／意外と</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>整然と並ぶ。</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>列の美しさに驚く。</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>S-033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>使える一言</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>依頼・許可・断り</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>やんわり断る</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>同僚（どうりょう）：今日（きょう）、飲（の）みに 行（い）きませんか。
+カイ：ありがとうございます。でも、今日（きょう）は ちょっと…。
+同僚：あ、用事（ようじ）ですか。
+カイ：ええ、また 今度（こんど） ぜひ お願（ねが）いします。
+——『ちょっと…』と 言葉（ことば）を にごすと、はっきり 言（い）わなくても「行（い）けない」と 伝（つた）わります。『また 今度（こんど）』で 次（つぎ）への 気持（きも）ちも 残（のこ）せます。</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Colleague: Want to go for a drink today? / Kai: Thank you. But today is a little... / Colleague: Oh, you have plans? / Kai: Yes—let's definitely do it another time. — By trailing off with 'chotto...,' you convey 'I can't' without saying it directly. 'Another time' leaves the door open for next time.</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>ちょっと…／また 今度／ぜひ</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>角を立てない断り。</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>魔法の言葉『ちょっと』。</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:2名</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>S-034</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>使える一言</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>気持ち・相づち</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>共感・はげます</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>友（とも）だち：最近（さいきん）、仕事（しごと）が 忙（いそが）しくて…。
+カイ：そっか、大変（たいへん）だね。
+友（とも）だち：うん、毎日（まいにち） 残業（ざんぎょう）なんだ。
+カイ：無理（むり）しないでね。体（からだ）に 気（き）を つけて。
+——『大変（たいへん）だね』『無理（むり）しないで』は、相手（あいて）の 気持（きも）ちに 寄（よ）り添（そ）う ひとことです。アドバイスより、まず 共感（きょうかん）が 大切（たいせつ）な ことも あります。</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Friend: Work has been so busy lately... / Kai: I see, that's tough. / Friend: Yeah, overtime every day. / Kai: Don't push yourself. Take care of yourself. — 'That's tough' and 'don't push yourself' are phrases that show empathy. Sometimes empathy matters more than advice.</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>大変だね／無理しないで／気を つけて</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>共感のひとこと。</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>励ましの定番フレーズ。</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:2名</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>S-035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>グルメ</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>お寿司の食べ方</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>お寿司（すし）は、はしでも 手（て）でも 食（た）べて いいです。しょうゆは、ネタ(=魚（さかな）)の ほうに 少（すこ）し つけます。ごはんに つけると、ごはんが くずれて しまうからです。わさびが 苦手（にがて）な 人（ひと）は、『さび抜（ぬ）きで』と たのめます。回転（かいてん）寿司（ずし）では、好（す）きな お皿（さら）を 取（と）り、最後（さいご）に お皿（さら）の 数（かず）で 計算（けいさん）します。</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>You may eat sushi with chopsticks or your hands. Dip a little soy sauce on the topping (the fish) side; if you dip the rice, it falls apart. If you don't like wasabi, you can ask for 'sabi-nuki' (without wasabi). At conveyor-belt sushi, you take the plates you like and pay at the end by the number of plates.</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>〜ても いい／〜から／さび抜きで</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>寿司の作法。</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>しょうゆの付け方に通な差。</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>S-036</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>グルメ</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>居酒屋で注文する</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>店員（てんいん）：ご注文（ちゅうもん）は お決（き）まりですか。
+カイ：とりあえず、生（なま）ビールを 二（ふた）つ ください。
+店員：はい、生（なま） 二（ふた）つ。お料理（りょうり）は？
+カイ：からあげと、枝豆（えだまめ）を お願（ねが）いします。
+店員：かしこまりました。
+——居酒屋（いざかや）では『とりあえず 生（なま）！』が 定番（ていばん）。飲（の）み物（もの）を 先（さき）に たのんで、料理（りょうり）は あとから 少（すこ）しずつ 注文（ちゅうもん）します。</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Staff: Are you ready to order? / Kai: For now, two draft beers, please. / Staff: Sure, two drafts. And food? / Kai: Fried chicken and edamame, please. / Staff: Certainly. — At izakaya, 'a draft for now!' is the classic move. You order drinks first and add dishes little by little.</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>とりあえず／〜を ください／お決まりですか</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>居酒屋の注文。</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>合言葉『とりあえず生』。</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:2名</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>S-037</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>グルメ</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ラーメンの種類</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の ラーメンには、たくさんの 種類（しゅるい）が あります。スープで 分（わ）けると、しょうゆ、塩（しお）、みそ、とんこつ などが 有名（ゆうめい）です。地域（ちいき）に よって 味（あじ）も ちがい、北海道（ほっかいどう）の みそラーメン、九州（きゅうしゅう）の とんこつラーメンは とくに 人気（にんき）です。麺（めん）の かたさや 味（あじ）の こさを 選（えら）べる お店（みせ）も 多（おお）く、自分（じぶん）好（ごの）みの 一杯（いっぱい）を 見（み）つけられます。</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Japanese ramen comes in many kinds. By soup, soy sauce, salt, miso, and tonkotsu (pork bone) are famous. Flavors differ by region—Hokkaido's miso ramen and Kyushu's tonkotsu ramen are especially popular. Many shops let you choose noodle firmness and flavor strength, so you can find your own perfect bowl.</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>〜で 分けると／〜によって／〜好み</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>ラーメンの多様さ。</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>自分好みの一杯探し。</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>S-038</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>グルメ</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>だしと「うま味」</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>和食（わしょく）の おいしさの 秘密（ひみつ）は「だし」に あります。こんぶや かつおぶしから とる だしには、「うま味（み）」と いう 味（あじ）が あります。これは、あまい・からい・すっぱい・にがい・しょっぱい に つづく「第五（だいご）の 味（あじ）」と 言（い）われ、今（いま）では 世界（せかい）でも『UMAMI』として 知（し）られています。だしが きいた みそ汁（しる）は、シンプルでも 深（ふか）い 味（あじ）が します。</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>The secret of washoku's deliciousness is 'dashi' (stock). Dashi made from kombu and bonito flakes has a taste called 'umami.' It's called the 'fifth taste' after sweet, spicy, sour, bitter, and salty, and is now known worldwide as 'UMAMI.' Miso soup with good dashi tastes deep even though it's simple.</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>〜に ある／〜と 言われ／〜が きく</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>うま味とだし。</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>世界に広がるUMAMI。</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>S-039</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>言葉遊び</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>今日の擬音語</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ぺこぺこ・ぐうぐう</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>おなかが すいた とき、日本語（にほんご）では『おなかが ぺこぺこ』と 言（い）います。とても すいて いる ようすです。おなかが 鳴（な）る 音（おと）は『ぐう〜』。たくさん 食（た）べて おなかが いっぱいに なると『ぱんぱん』。眠（ねむ）くて たまらない ときは『うとうと』します。気持（きも）ちや 体（からだ）の ようすを、音（おと）で 表（あらわ）す のが 擬音語（ぎおんご）の おもしろさです。</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>When you're hungry, in Japanese you say your stomach is 'peko-peko'—the state of being very hungry. The sound of a growling stomach is 'guu~.' When you've eaten a lot and are full, it's 'pan-pan.' When you're terribly sleepy, you 'uto-uto' (doze off). Expressing feelings and bodily states with sounds is the fun of onomatopoeia.</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>ぺこぺこ／ぐう／ぱんぱん／うとうと</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>体調の擬音語。</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>音で気分まるわかり。</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>S-040</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>言葉遊び</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>ことわざ・慣用句</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>猿も木から落ちる</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>『猿（さる）も 木（き）から 落（お）ちる』は、有名（ゆうめい）な ことわざです。木登（きのぼ）りが 上手（じょうず）な 猿（さる）でも、ときには 木（き）から 落（お）ちる。つまり、どんなに 得意（とくい）な 人（ひと）でも、失敗（しっぱい）する ことが ある、という 意味（いみ）です。にた ことわざに『かっぱの 川流（かわなが）れ』『弘法（こうぼう）も 筆（ふで）の あやまり』が あります。失敗（しっぱい）した 友（とも）だちを なぐさめる ときに 使（つか）えます。</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>'Even monkeys fall from trees' is a famous proverb. Even monkeys, who are good climbers, sometimes fall. In other words, even the most skilled person can make mistakes. Similar proverbs are 'even a kappa gets swept down the river' and 'even Kobo makes a slip of the brush.' You can use it to comfort a friend who has failed.</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>〜も 〜から 落ちる／つまり／〜ことが ある</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>失敗は誰にでも。</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>落ち込む友へ贈る一言。</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2118,7 +3471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3822,6 +5175,539 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>L-023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ミステリー</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>消えた最終電車</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>夜（よる）11時（じ）50分（ぷん）、駅員（えきいん）の 木村（きむら）さんは おかしな ことに 気（き）づいた。
+木村：あれ？ さっきまで ホームに いた 女（おんな）の 人（ひと）、どこへ 行（い）ったんだ…。
+終電（しゅうでん）は まだ 来（き）ていない。改札（かいさつ）も 通（とお）っていない。なのに、ホームには 誰（だれ）も いない。
+木村：かばんだけが、ベンチに 残（のこ）っている…。
+次（つぎ）の 朝（あさ）、かばんの 中（なか）から 一枚（いちまい）の 古（ふる）い 切符（きっぷ）が 見（み）つかった。日付（ひづけ）は——30年（ねん）前（まえ）だった。
+（つづく）</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>11:50 p.m. Station attendant Kimura noticed something strange. Kimura: Huh? The woman who was on the platform just now—where did she go...? The last train hasn't come yet. She didn't pass the gate. And yet, no one is on the platform. Kimura: Only a bag is left on the bench... The next morning, an old ticket was found inside the bag. The date was—30 years ago. (To be continued)</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>〜に 気づいた／なのに／〜だった</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>続きが気になる導入。</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>30年前の切符の謎。</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:ナレーション/駅員</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>L-024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>黒部ダムをつくった男たち</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>昭和（しょうわ）の 時代（じだい）、富山（とやま）の 山（やま）おくに、巨大（きょだい）な ダムを つくる 計画（けいかく）が あった。黒部（くろべ）ダムである。けわしい 山（やま）、冷（つめ）たい 水（みず）、そして 固（かた）い 岩（いわ）。工事（こうじ）は 想像（そうぞう）を こえる 困難（こんなん）の 連続（れんぞく）だった。とくに トンネルを ほる 作業（さぎょう）では、地下水（ちかすい）が ふき出（だ）し、何度（なんど）も 工事（こうじ）が 止（と）まった。それでも 作業員（さぎょういん）たちは あきらめなかった。7年（ねん）の 月日（つきひ）と、のべ 1000万人（まんにん）の 力（ちから）で、ダムは ついに 完成（かんせい）した。今（いま）も 黒部（くろべ）の 水（みず）は、人々（ひとびと）の 暮（く）らしを ささえている。</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>In the Showa era, there was a plan to build a huge dam deep in the mountains of Toyama: the Kurobe Dam. Steep mountains, cold water, and hard rock—construction was a series of difficulties beyond imagination. Especially when digging the tunnel, groundwater gushed out and work stopped many times. Still, the workers never gave up. With seven years and the effort of ten million people in total, the dam was finally completed. Even now, Kurobe's water supports people's lives.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>〜を こえる／何度も／それでも</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>困難に挑む実話。</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>不可能を可能にした執念。</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>L-025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>新幹線――夢の超特急</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>1964年（ねん）、東京（とうきょう）と 大阪（おおさか）を むすぶ「新幹線（しんかんせん）」が 走（はし）り はじめた。当時（とうじ）、時速（じそく）200キロを こえる 電車（でんしゃ）は、世界（せかい）の どこにも なかった。『そんな スピードは あぶない』と 多（おお）くの 人（ひと）が 反対（はんたい）した。技術者（ぎじゅつしゃ）たちは、空気（くうき）の 力（ちから）や 線路（せんろ）の カーブを 何度（なんど）も 計算（けいさん）し、安全（あんぜん）の ために 知恵（ちえ）を しぼった。開業（かいぎょう）の 日（ひ）、新幹線（しんかんせん）は 一度（いちど）の 事故（じこ）も なく 走（はし）りきった。夢（ゆめ）の 超特急（ちょうとっきゅう）は、日本（にほん）の 誇（ほこ）りに なった。</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>In 1964, the Shinkansen connecting Tokyo and Osaka began running. At the time, no train anywhere in the world exceeded 200 km/h. 'Such speed is dangerous,' many people opposed. Engineers calculated air resistance and track curves again and again, racking their brains for safety. On opening day, the Shinkansen ran the whole way without a single accident. The dream super-express became a source of pride for Japan.</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>〜を こえる／〜の ために／〜きった</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>世界初の高速鉄道。</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>反対を覆した技術の結晶。</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>L-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>青い光をもとめて</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>赤（あか）と 緑（みどり）の 光（ひかり）は できても、「青（あお）い 光（ひかり）」を 出（だ）す LEDだけは、だれにも 作（つく）れなかった。『20世紀（せいき）中（じゅう）には 無理（むり）だ』とも 言（い）われた。日本（にほん）の ある 研究者（けんきゅうしゃ）は、小（ちい）さな 会社（かいしゃ）で、たった 一人（ひとり）、何千回（なんぜんかい）も 実験（じっけん）を くりかえした。失敗（しっぱい）、また 失敗（しっぱい）。それでも 手（て）を 止（と）めなかった。ついに 青（あお）い 光（ひかり）が ともった 瞬間（しゅんかん）、世界（せかい）の 明（あ）かりは 変（か）わった。白（しろ）い LEDが 生（う）まれ、街（まち）も 家（いえ）も 明（あか）るく なった。その 功績（こうせき）は、のちに ノーベル賞（しょう）に かがやいた。</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Red and green light were possible, but a blue-light LED was something no one could make. 'It's impossible within the 20th century,' they said. One Japanese researcher, alone at a small company, repeated experiments thousands of times. Failure, and failure again. Still he never stopped. The moment blue light finally lit up, the world's lighting changed. White LEDs were born, brightening streets and homes. The achievement later shone with a Nobel Prize.</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>〜だけは／くりかえした／〜瞬間</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>青色LEDの挑戦。</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>孤独な執念がノーベル賞に。</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>L-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>昔話</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>浦島太郎</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>むかしむかし、浦島太郎（うらしまたろう）という 若者（わかもの）が いました。ある 日（ひ）、いじめられている 亀（かめ）を 助（たす）けて あげました。お礼（れい）に、亀（かめ）は 太郎（たろう）を 海（うみ）の 中（なか）の「竜宮城（りゅうぐうじょう）」へ つれて 行（い）きました。そこは 美（うつく）しい おとめ「乙姫（おとひめ）」が すむ、ゆめのような 場所（ばしょ）でした。楽（たの）しい 日々（ひび）を すごし、太郎（たろう）が 家（いえ）に 帰（かえ）ると——村（むら）は すっかり 変（か）わって いました。なんと、何百年（なんびゃくねん）もの 時（とき）が すぎて いたのです。</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Long ago, there was a young man named Urashima Taro. One day, he rescued a turtle that was being bullied. In return, the turtle took Taro to the 'Dragon Palace' beneath the sea. It was a dreamlike place where the beautiful maiden 'Otohime' lived. After spending happy days there, Taro returned home—but the village had completely changed. Astonishingly, hundreds of years had passed.</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>〜て あげる／〜のような／なんと</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>助けた恩と時の流れ。</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>玉手箱の結末は…?</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>L-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>昔話</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>かぐや姫</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>むかし、竹（たけ）を とって 暮（く）らす おじいさんが いました。ある 日（ひ）、光（ひか）る 竹（たけ）の 中（なか）から、小（ちい）さな 女（おんな）の 子（こ）が 生（う）まれました。「かぐや姫（ひめ）」と 名（な）づけられた その 子（こ）は、月（つき）のように 美（うつく）しく 育（そだ）ちました。やがて、たくさんの 男（おとこ）たちが 結婚（けっこん）を もうし込（こ）みましたが、姫（ひめ）は 首（くび）を たてに ふりません。実（じつ）は、かぐや姫（ひめ）は 月（つき）の 世界（せかい）から 来（き）た 人（ひと）でした。満月（まんげつ）の 夜（よる）、姫（ひめ）は 月（つき）へ 帰（かえ）って いきました。</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Long ago, there was an old man who made his living cutting bamboo. One day, a tiny girl was born from a glowing stalk of bamboo. Named 'Kaguya-hime,' she grew as beautiful as the moon. In time, many men proposed marriage, but the princess would not nod yes. In fact, Kaguya-hime was a person from the world of the moon. On the night of the full moon, she returned to the moon.</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>〜の中から／〜のように／やがて</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>竹から生まれた姫。</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>日本最古の物語の一つ。</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>L-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>昔話</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>鶴の恩返し</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>さむい 冬（ふゆ）の 日（ひ）、ある 男（おとこ）が、わなに かかった 鶴（つる）を 助（たす）けました。その 夜（よる）、美（うつく）しい 女（おんな）の 人（ひと）が 家（いえ）を たずねて きて、男（おとこ）の 妻（つま）に なりました。妻（つま）は『けっして 見（み）ないで ください』と 言（い）って、部屋（へや）で 布（ぬの）を おりました。その 布（ぬの）は とても 高（たか）く 売（う）れました。ある 日（ひ）、男（おとこ）が こっそり のぞくと——そこには、自分（じぶん）の 羽根（はね）を ぬいて 布（ぬの）を おる 鶴（つる）の 姿（すがた）が ありました。正体（しょうたい）を 知（し）られた 妻（つま）は、空（そら）へ 飛（と）んで 行（い）きました。</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>On a cold winter day, a man rescued a crane caught in a trap. That night, a beautiful woman visited his house and became his wife. She said, 'Please never look,' and wove cloth in a room. The cloth sold for a very high price. One day, when the man secretly peeked—there was the crane, plucking its own feathers to weave the cloth. Once her true form was known, the wife flew away into the sky.</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>〜を 助ける／けっして〜ないで／〜と …が ある</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>約束と恩返し。</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>見てはいけない約束の結末。</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>L-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>昔話</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>笠地蔵</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>年（とし）の くれ、まずしい おじいさんが、町（まち）へ 笠（かさ）を 売（う）りに 行（い）きました。でも、一（ひと）つも 売（う）れません。帰（かえ）り道（みち）、雪（ゆき）の 中（なか）に 立（た）つ 六（む）つの お地蔵（じぞう）さまを 見（み）つけました。『さむそうだ』と、おじいさんは 売（う）り物（もの）の 笠（かさ）を お地蔵（じぞう）さまに かぶせて あげました。一（ひと）つ 足（た）りないので、自分（じぶん）の 手（て）ぬぐいを かけました。その 夜（よる）、ふしぎな ことが おきました。朝（あさ）、戸（と）を 開（あ）けると、米（こめ）や もちが 山（やま）のように 置（お）いて あったのです。</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>At year's end, a poor old man went to town to sell straw hats. But not one sold. On the way home, he found six Jizo statues standing in the snow. 'They look cold,' he said, and placed the hats he had been selling on the statues. One was short, so he used his own hand towel. That night, something mysterious happened. In the morning, when he opened the door, rice and mochi were piled up like a mountain.</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>〜そうだ／〜て あげる／〜のように</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>親切が返ってくる話。</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>心温まる年越しの奇跡。</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -1646,14 +1646,10 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>言葉遊び</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>今日の擬音語</t>
-        </is>
-      </c>
+          <t>擬音語</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>ふわふわ</t>
@@ -1716,14 +1712,10 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>言葉遊び</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>ことわざ・慣用句</t>
-        </is>
-      </c>
+          <t>ことわざ</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>猫の手も借りたい</t>
@@ -1786,14 +1778,10 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>言葉遊び</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
           <t>カタカナ語</t>
         </is>
       </c>
+      <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>和製英語に気をつけて</t>
@@ -3333,14 +3321,10 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>言葉遊び</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>今日の擬音語</t>
-        </is>
-      </c>
+          <t>擬音語</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr">
         <is>
           <t>ぺこぺこ・ぐうぐう</t>
@@ -3403,14 +3387,10 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>言葉遊び</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>ことわざ・慣用句</t>
-        </is>
-      </c>
+          <t>ことわざ</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>猿も木から落ちる</t>
@@ -4021,7 +4001,7 @@
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>司会（しかい）：今日（きょう）の ゲストは、日本（にほん）で 勉強（べんきょう）している カイさんです。日本に 来て どのくらいですか。
-カイ：2年（ねん）です。
+カイ：半年（はんとし）くらいです。
 司会：日本で 一番（いちばん）好（す）きな ものは？
 カイ：温泉（おんせん）です。とても 気持（きも）ちが いいです。
 司会：これから 何（なに）を したいですか。
@@ -4030,11 +4010,11 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Host: Today's guest is Kai, who is studying in Japan. How long have you been in Japan? / Kai: Two years. / Host: What's your favorite thing in Japan? / Kai: Hot springs. They feel so good. / Host: What do you want to do from now on? / Kai: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
+          <t>Host: Today's guest is Kai, who is studying in Japan. How long have you been in Japan? / Kai: About half a year. / Host: What's your favorite thing in Japan? / Kai: Hot springs. They feel so good. / Host: What do you want to do from now on? / Kai: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -4541,12 +4521,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>カイの日常</t>
+          <t>日本生活スタート</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>友だちができた</t>
+          <t>はじめての友だち（ミナ）</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -4561,22 +4541,22 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）日本（にほん）に 来（き）た ばかりの ころ、カイは 友（とも）だちが いなくて さびしかった。ある日（ひ）、日本語（にほんご）の 教室（きょうしつ）で…
-クラスメート：あ、その ペン、いいね。どこで 買（か）ったの？
+          <t>（ナレーション）日本（にほん）に 来（き）た ばかりの ころ、カイは 友（とも）だちが いなくて さびしかった。ある日（ひ）、日本語（にほんご）の 教室（きょうしつ）で、となりの 席（せき）の 人（ひと）が 話（はな）しかけてきた。
+ミナ：あ、その ペン、いいね。どこで 買（か）ったの？
 カイ：えっ、これ？ 駅前（えきまえ）の お店（みせ）です。
-クラスメート：へえ。ねえ、よかったら いっしょに お昼（ひる）、食（た）べない？
+ミナ：へえ。わたし、ミナ。同（おな）じ クラスだね。よかったら いっしょに お昼（ひる）、食（た）べない？
 カイ：いいんですか？ うれしいです！
-（ナレーション）その 一言（ひとこと）が、とても うれしかった。
+（ナレーション）はじめての 友（とも）だち、ミナ。その 一言（ひとこと）が、とても うれしかった。
 カイ：（心の声）勇気（ゆうき）を 出（だ）して よかった…！
-（ナレーション）今（いま）では、休（やす）みの 日（ひ）に いっしょに 出（で）かける 仲（なか）だ。</t>
+（ナレーション）この 日（ひ）から、ミナは カイの 大切（たいせつ）な 友（とも）だちに なった。</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>(Narration) Just after coming to Japan, Kai had no friends and felt lonely. One day, in Japanese class... / Classmate: Oh, that pen's nice. Where'd you buy it? / Kai: Huh, this? At the shop in front of the station. / Classmate: Huh. Hey, if you'd like, want to have lunch together? / Kai: Really? I'd love to! / (Narration) That one phrase made him so happy. / Kai: (inner voice) I'm so glad I found the courage...! / (Narration) Now they're close enough to go out together on days off.</t>
+          <t>(Narration) Just after coming to Japan, Kai had no friends and felt lonely. One day, in Japanese class, the person next to him struck up a conversation. / Mina: Oh, that pen's nice. Where'd you buy it? / Kai: Huh, this? At the shop in front of the station. / Mina: Huh. I'm Mina. We're in the same class. If you'd like, want to have lunch together? / Kai: Really? I'd love to! / (Narration) His first friend, Mina. That one phrase made him so happy. / Kai: (inner voice) I'm so glad I found the courage...! / (Narration) From this day, Mina became Kai's dear friend.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -4586,17 +4566,17 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>友だち作りの会話。会話表現「えっ/へえ/ねえ」。誘いの「〜ない?」。</t>
+          <t>相棒ミナとの出会い。会話表現「えっ/へえ/ねえ」。誘いの「〜ない?」。</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>一歩ふみ出す勇気＝共感。</t>
+          <t>相棒ミナ デビュー＝旅編への伏線。</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーター/カイ/クラスメート</t>
+          <t>多声TTS:ナレーター/カイ/ミナ</t>
         </is>
       </c>
     </row>

--- a/コンテンツ.xlsx
+++ b/コンテンツ.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3440,6 +3440,666 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>S-041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>ことわざ</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>石の上にも三年</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>『石（いし）の 上（うえ）にも 三年（さんねん）』は、がんばりを 教（おし）える ことわざです。冷（つめ）たい 石（いし）の 上（うえ）でも、三年（さんねん）すわり 続（つづ）ければ、あたたかく なる。つまり、つらい ことでも、あきらめずに 続（つづ）ければ、いつか 実（みの）る、という 意味（いみ）です。日本語（にほんご）の 勉強（べんきょう）も 同（おな）じ。すぐに 結果（けっか）が 出（で）なくても、毎日（まいにち） 少（すこ）しずつ 続（つづ）ければ、きっと 上手（じょうず）に なります。</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>'Even on a stone, three years' is a proverb that teaches perseverance. Even on a cold stone, if you keep sitting for three years, it grows warm. In other words, even hard things, if you keep at them without giving up, will eventually bear fruit. Studying Japanese is the same. Even if results don't come right away, if you keep going a little each day, you'll surely improve.</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>〜ば／つまり／〜ても</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>継続は力なり。</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>学習者への応援。</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>S-042</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>ことわざ</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>花より団子</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>『花（はな）より 団子（だんご）』は、おもしろい ことわざです。きれいな 桜（さくら）の 花（はな）を 見（み）る より、おいしい 団子（だんご）を 食（た）べる ほうが いい。つまり、見（み）た目（め）の 美（うつく）しさ より、役（やく）に 立（た）つ ものや 実（じつ）の ある ものを 選（えら）ぶ、という 意味（いみ）です。お花見（はなみ）で、景色（けしき）より お弁当（べんとう）に 夢中（むちゅう）な 人（ひと）を 見（み）たら、『花より団子だね』と 言（い）えます。</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>'Dumplings over flowers' is a fun proverb. Rather than viewing the beautiful cherry blossoms, eating tasty dumplings is better. In other words, it means choosing what's useful or substantial over mere appearance. If at a cherry-blossom party you see someone more absorbed in their bento than the scenery, you can say 'dumplings over flowers.'</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>〜より 〜ほうが／つまり／〜に 夢中</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>実利を取るたとえ。</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>食いしん坊あるある。</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>S-043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>ことわざ</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>七転び八起き</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>読み物</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>『七転（ななころ）び 八起（やお）き』は、何度（なんど） 失敗（しっぱい）しても 立（た）ち上（あ）がる 強（つよ）さを 表（あらわ）す ことわざです。七回（ななかい） ころんでも、八回（はちかい） 起（お）き上（あ）がる。人生（じんせい）には うまく いかない ことも 多（おお）いけれど、そのたびに 起（お）き上（あ）がれば いい、という 前向（まえむ）きな 言葉（ことば）です。だるまの 人形（にんぎょう）は、この 心（こころ）を 表（あらわ）しています。</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>'Fall seven times, get up eight' is a proverb expressing the strength to rise no matter how many times you fail. Even if you fall seven times, you get up eight. Life has many things that don't go well, but it's a positive saying that you can just get up each time. The daruma doll embodies this spirit.</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>何度〜ても／そのたびに／〜ば いい</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>不屈の精神。</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>だるまに込めた心。</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>S-044</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>カタカナ語</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>マンションとアパート</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）で「マンション」と 言（い）うと、鉄筋（てっきん）の りっぱな 集合住宅（しゅうごうじゅうたく）の ことです。英語（えいご）の「mansion」（大（おお）きな 屋敷（やしき））とは 意味（いみ）が ちがいます。木造（もくぞう）や 小（ちい）さめの 建物（たてもの）は「アパート」と 呼（よ）びます。部屋（へや）を 探（さが）す とき、この ちがいを 知（し）っておくと 便利（べんり）です。</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>In Japan, 'mansion' means a fine reinforced-concrete apartment building. It differs from the English 'mansion' (a large estate). Wooden or smaller buildings are called 'apato.' When looking for a place, it's handy to know this difference.</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>〜と 言うと／〜とは ちがう／〜ておくと 便利</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>和製英語の落とし穴。</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>部屋探しで役立つ。</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>S-045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>カタカナ語</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>バイキングは食べ放題</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>レストランで「バイキング」と 言（い）えば、好（す）きな だけ 食（た）べられる「食（た）べ放題（ほうだい）」の ことです。これは 日本（にほん）で 生（う）まれた 言（い）い方（かた）で、英語（えいご）では「buffet（ビュッフェ）」と 言（い）います。ホテルの 朝食（ちょうしょく）で よく 見（み）ます。料理（りょうり）を 取（と）りすぎて、おなかが ぱんぱんに なる 人（ひと）も います。</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>At a restaurant, 'baikingu' (Viking) means an all-you-can-eat 'buffet.' This expression was born in Japan; in English it's 'buffet.' You often see it at hotel breakfasts. Some people take too much food and end up stuffed.</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>〜と 言えば／〜放題／取りすぎる</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>和製英語バイキング。</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>食べ放題の誘惑。</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>S-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>カタカナ語</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>コンセントとプラグ</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>電気（でんき）の さしこみ口（ぐち）を、日本（にほん）では「コンセント」と 言（い）います。でも 英語（えいご）では「outlet」や「socket」。「consent」は 英語（えいご）で「同意（どうい）」の 意味（いみ）なので、まったく ちがいます。さしこむ 方（ほう）は「プラグ」。海外（かいがい）の 製品（せいひん）を 使（つか）う ときは、形（かたち）が 合（あ）うか 確（たし）かめましょう。</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>In Japan, an electrical socket is called 'konsento.' But in English it's 'outlet' or 'socket.' 'Consent' in English means agreement, so it's completely different. The part you plug in is the 'plug.' When using overseas products, check whether the shape fits.</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>〜では 〜と 言う／〜とは ちがう／確かめましょう</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>意味が全然違う和製英語。</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>海外旅行で注意。</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>S-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>カタカナ語</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>「サービス」はただ？</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>日本（にほん）の お店（みせ）で「これ、サービスです」と 言（い）われたら、「無料（むりょう）」「おまけ」の 意味（いみ）です。英語（えいご）の「service」（仕事・接客）とは 少（すこ）し ちがう 使（つか）い方（かた）です。ほかにも「アフターサービス」（修理（しゅうり）などの 対応（たいおう））など、日本（にほん）ならではの 使（つか）い方（かた）が あります。「サービスしますよ」と 言（い）われたら、少（すこ）し お得（とく）な サインです。</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>If a Japanese shop says 'this is service,' it means 'free' or 'a freebie.' It's a slightly different usage from the English 'service' (work/hospitality). There are also Japan-specific uses like 'after-service' (handling repairs, etc.). If you hear 'I'll give you a service,' it's a sign of a little bargain.</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>〜と 言われたら／〜とは 少し ちがう／〜ならでは</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>得する和製英語。</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>値引きのサイン。</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>S-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>擬音語</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>わくわく・どきどき</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>楽（たの）しみで 心（こころ）が おどる とき、日本語（にほんご）では『わくわく』します。旅行（りょこう）の 前（まえ）の 夜（よる）は、わくわくして 眠（ねむ）れません。きんちょうや こわさで 胸（むね）が 速（はや）く なる ときは『どきどき』。はじめての 面接（めんせつ）は どきどきします。気持（きも）ちの 高（たか）まりを、音（おと）で 表（あらわ）す ことが できます。</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>When your heart dances with anticipation, in Japanese you go 'waku-waku.' The night before a trip, you're so excited you can't sleep. When your chest beats fast from nerves or fear, it's 'doki-doki.' A first interview makes you doki-doki. You can express rising emotions with sound.</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>わくわく／どきどき／〜して 〜ない</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>感情の擬音語。</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>気分が伝わる音。</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>S-049</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>擬音語</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ぴかぴか・つるつる</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>きれいに みがかれて 光（ひか）る ようすは『ぴかぴか』。そうじの あとの 床（ゆか）は ぴかぴかです。表面（ひょうめん）が なめらかで すべる ようすは『つるつる』。うどんを つるつる 食（た）べる、と 言（い）えば、勢（いきお）いよく すする ようすです。同（おな）じ つるつるでも、氷（こおり）は すべって あぶない。手（て）ざわりや 様子（ようす）を 音（おと）で 表（あらわ）します。</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Something polished and shining is 'pika-pika.' The floor after cleaning is pika-pika. A smooth, slippery surface is 'tsuru-tsuru.' 'Eating udon tsuru-tsuru' means slurping it up vigorously. The same tsuru-tsuru, but ice is slippery and dangerous. You express texture and appearance with sound.</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>ぴかぴか／つるつる／〜と 言えば</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>質感の擬音語。</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>音でツヤ・なめらかさ。</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>S-050</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>短文</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>擬音語</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ざあざあ・しとしと</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>雨（あめ）の ふり方（かた）も、音（おと）で 言（い）い分（わ）けます。強（つよ）く たくさん ふる ときは『ざあざあ』。しずかに 細（こま）かく ふる ときは『しとしと』。台風（たいふう）の 日（ひ）は ざあざあ、つゆの 季節（きせつ）は しとしと。雷（かみなり）が 鳴（な）る ときは『ごろごろ』。天気（てんき）の 様子（ようす）が、音（おと）だけで 伝（つた）わります。</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Even how rain falls is distinguished by sound. Heavy, abundant rain is 'zaa-zaa.' Quiet, fine rain is 'shito-shito.' A typhoon day is zaa-zaa; the rainy season is shito-shito. When thunder rumbles, it's 'goro-goro.' The weather's mood comes across through sound alone.</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>ざあざあ／しとしと／ごろごろ</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>天気の擬音語。</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>雨の強さを音で。</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>1話者・朗読</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3451,7 +4111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4076,20 +4736,20 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>A：週末（しゅうまつ）、どうだった？
-B：友（とも）だちと 海（うみ）に 行（い）ったよ。すごく きれいだった！
-A：いいなあ。私（わたし）は 一日中（いちにちじゅう）、家（いえ）で ドラマを 見（み）てた。
-B：それも いいよね。何（なに）の ドラマ？
-A：日本（にほん）の 恋愛（れんあい）ドラマ。じつは 日本語の 勉強（べんきょう）にも なるんだ。
-B：へえ、いいね！</t>
+          <t>ケンタ：週末（しゅうまつ）、どうだった？
+カイ：友（とも）だちの ミナと 海（うみ）に 行（い）ったよ。すごく きれいだった！
+ケンタ：いいなあ。おれは 一日中（いちにちじゅう）、家（いえ）で ドラマを 見（み）てた。
+カイ：それも いいね。何（なに）の ドラマ？
+ケンタ：日本（にほん）の 恋愛（れんあい）ドラマ。じつは 日本語の 勉強（べんきょう）にも なるんだぜ。
+カイ：へえ、いいね！</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>A: How was your weekend? / B: I went to the beach with friends. It was so beautiful! / A: Nice. I watched dramas at home all day. / B: That's good too. What drama? / A: A Japanese romance drama. Actually it's good Japanese study too. / B: Oh, nice!</t>
+          <t>Kenta: How was your weekend? / Kai: I went to the beach with my friend Mina. It was so beautiful! / Kenta: Nice. I watched dramas at home all day. / Kai: That's good too. What drama? / Kenta: A Japanese romance drama. Actually it's good Japanese study too. / Kai: Oh, nice!</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -4099,17 +4759,17 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>友だち同士の自然な雑談。</t>
+          <t>相棒ケンタとカイのゆるい雑談(再登場)。</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>ゆるい会話＝多聴に最適。</t>
+          <t>くだけた会話＝多聴に最適。</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:友人2人</t>
+          <t>多声TTS:ケンタ/カイ</t>
         </is>
       </c>
     </row>
@@ -4230,20 +4890,20 @@
         <is>
           <t>（ナレーション）引（ひ）っ越（こ）しの 次（つぎ）の 日（ひ）。カイは ゴミぶくろを 持（も）って、こまっていた。
 カイ：あれ？ ゴミは どこに 出（だ）せば いいんだろう…。
-（ナレーション）ちょうど、となりの 人（ひと）が 通（とお）りかかった。
+（ナレーション）ちょうど、近所（きんじょ）の 田中（たなか）さんが 通（とお）りかかった。世話（せわ）ずきな、この あたりの 大家（おおや）さんだ。
 カイ：あの、すみません。ゴミの 出（だ）し方（かた）が わからなくて…。
-となりの人：ああ、燃（も）えるゴミは 月曜（げつよう）と 木曜（もくよう）ですよ。朝（あさ）8時（じ）までに、そこの 角（かど）に 出（だ）してね。
+田中さん：ああ、燃（も）えるゴミは 月曜（げつよう）と 木曜（もくよう）ですよ。朝（あさ）8時（じ）までに、そこの 角（かど）に 出（だ）してね。
 カイ：そうなんですね！ ありがとうございます。助（たす）かりました。
-となりの人：困（こま）ったら いつでも 聞（き）いてね。
-（ナレーション）カイは ほっとした。「日本（にほん）の 人（ひと）は 親切（しんせつ）だなあ」。</t>
+田中さん：困（こま）ったら いつでも 聞（き）いてね。
+（ナレーション）カイは ほっとした。「田中（たなか）さん、親切（しんせつ）だなあ。心強（こころづよ）いな」。</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>(Narration) The day after moving. Kai stood there holding a trash bag, troubled. / Kai: Huh? Where am I supposed to put the trash...? / (Narration) Just then, a neighbor passed by. / Kai: Um, excuse me. I don't know how to sort the trash... / Neighbor: Ah, burnable trash is Monday and Thursday. Put it at that corner by 8 a.m. / Kai: Oh, I see! Thank you, that helps. / Neighbor: Ask me anytime you're stuck. / (Narration) Kai felt relieved. 'Japanese people are so kind.'</t>
+          <t>(Narration) The day after moving. Kai stood there holding a trash bag, troubled. / Kai: Huh? Where am I supposed to put the trash...? / (Narration) Just then, Tanaka-san, the caring landlady of the area, passed by. / Kai: Um, excuse me. I don't know how to sort the trash... / Tanaka: Ah, burnable trash is Monday and Thursday. Put it at that corner by 8 a.m. / Kai: Oh, I see! Thank you, that helps. / Tanaka: Ask me anytime you're stuck. / (Narration) Kai felt relieved. 'Tanaka-san is so kind. That's reassuring.'</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -4253,17 +4913,17 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>近所での会話＋気づき。会話表現「あれ?/〜なんですね/〜てね」。</t>
+          <t>近所のメンター田中さん デビュー。会話表現「あれ?/〜なんですね/〜てね」。</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>短文「生活力」と再会＝らせん。</t>
+          <t>世話役 田中さん＝文化/本音への伏線。</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーター/カイ/近所の人</t>
+          <t>多声TTS:ナレーター/カイ/田中さん</t>
         </is>
       </c>
     </row>
@@ -4541,22 +5201,22 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）日本（にほん）に 来（き）た ばかりの ころ、カイは 友（とも）だちが いなくて さびしかった。ある日（ひ）、日本語（にほんご）の 教室（きょうしつ）で、となりの 席（せき）の 人（ひと）が 話（はな）しかけてきた。
+          <t>（ナレーション）学校（がっこう）が 始（はじ）まって 数日（すうじつ）。まだ クラスに なれない カイに、同（おな）じ クラスの ミナが 話（はな）しかけてきた。
 ミナ：あ、その ペン、いいね。どこで 買（か）ったの？
 カイ：えっ、これ？ 駅前（えきまえ）の お店（みせ）です。
-ミナ：へえ。わたし、ミナ。同（おな）じ クラスだね。よかったら いっしょに お昼（ひる）、食（た）べない？
+ミナ：へえ。ねえ、よかったら いっしょに お昼（ひる）、食（た）べない？
 カイ：いいんですか？ うれしいです！
-（ナレーション）はじめての 友（とも）だち、ミナ。その 一言（ひとこと）が、とても うれしかった。
+（ナレーション）その 一言（ひとこと）が、とても うれしかった。
 カイ：（心の声）勇気（ゆうき）を 出（だ）して よかった…！
-（ナレーション）この 日（ひ）から、ミナは カイの 大切（たいせつ）な 友（とも）だちに なった。</t>
+（ナレーション）この 日（ひ）から、ミナは カイの いちばんの 友（とも）だちに なった。</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>(Narration) Just after coming to Japan, Kai had no friends and felt lonely. One day, in Japanese class, the person next to him struck up a conversation. / Mina: Oh, that pen's nice. Where'd you buy it? / Kai: Huh, this? At the shop in front of the station. / Mina: Huh. I'm Mina. We're in the same class. If you'd like, want to have lunch together? / Kai: Really? I'd love to! / (Narration) His first friend, Mina. That one phrase made him so happy. / Kai: (inner voice) I'm so glad I found the courage...! / (Narration) From this day, Mina became Kai's dear friend.</t>
+          <t>(Narration) A few days after school started. To Kai, who still hadn't settled into class, Mina—a classmate—struck up a conversation. / Mina: Oh, that pen's nice. Where'd you buy it? / Kai: Huh, this? At the shop in front of the station. / Mina: Huh. Hey, if you'd like, want to have lunch together? / Kai: Really? I'd love to! / (Narration) That one phrase made him so happy. / Kai: (inner voice) I'm so glad I found the courage...! / (Narration) From this day, Mina became Kai's best friend.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -4566,12 +5226,12 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>相棒ミナとの出会い。会話表現「えっ/へえ/ねえ」。誘いの「〜ない?」。</t>
+          <t>相棒ミナと仲よくなる回。会話表現「えっ/へえ/ねえ」。誘いの「〜ない?」。</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>相棒ミナ デビュー＝旅編への伏線。</t>
+          <t>相棒ミナ＝旅編への伏線。</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -5688,6 +6348,158 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>L-031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>カイの物語</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>日本生活スタート</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>バイトを始める</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>（ナレーション）カイは、駅前（えきまえ）の カフェで バイトを 始（はじ）めた。初日（しょにち）、同（おな）じ シフトの 男（おとこ）の 子（こ）が 声（こえ）を かけてきた。
+ケンタ：あ、新（あたら）しい 人（ひと）？ おれ、ケンタ。よろしく！
+カイ：カイです。よろしく お願（ねが）いします。
+ケンタ：かたいなあ（笑）。タメで いいよ。わからない こと あったら、何（なん）でも 聞（き）いて。
+カイ：ありがとう。じゃあ…レジ、まだ ちょっと こわくて。
+ケンタ：だいじょうぶ だいじょうぶ。最初（さいしょ）は みんな そう。おれが ついてる から！
+（ナレーション）ケンタの 明（あか）るさに、カイの きんちょうは すっと ほどけた。「日本人（にほんじん）の 友（とも）だち、第一号（だいいちごう）だ」。</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>(Narration) Kai started a part-time job at a cafe by the station. On day one, a guy on the same shift spoke to him. / Kenta: Oh, the new person? I'm Kenta. Nice to meet you! / Kai: I'm Kai. Pleased to meet you. / Kenta: So formal, ha. You can be casual with me. If there's anything you don't get, just ask. / Kai: Thanks. Then... the register still scares me a bit. / Kenta: It's fine, it's fine. Everyone's like that at first. I've got your back! / (Narration) Kenta's brightness loosened Kai's nerves at once. 'My first Japanese friend.'</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>タメで いい／〜たら 聞いて／ついてる</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>日本人の友ケンタ デビュー。くだけた会話表現。</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>相棒その2＝フリートークへの伏線。</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:ナレーター/カイ/ケンタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>L-032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>カイの物語</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>日本生活スタート</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>日本語学校の初日</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>（ナレーション）日本語（にほんご）学校（がっこう）の 初日（しょにち）。教室（きょうしつ）に 入（はい）ると、先生（せんせい）が にっこり わらった。
+さくら先生：みなさん、はじめまして。担任（たんにん）の さくらです。今日（きょう）から いっしょに がんばりましょう。
+カイ：（心の声）やさしそうな 先生（せんせい）で よかった…。
+さくら先生：では、となりの 人（ひと）と あいさつを して みましょう。
+ミナ：はじめまして、ミナです。
+カイ：カイです。よろしく お願（ねが）いします。
+（ナレーション）さくら先生（せんせい）の ていねいな 日本語（にほんご）と、ミナの 笑顔（えがお）。カイの 新（あたら）しい 毎日（まいにち）は、ここから 始（はじ）まった。</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>(Narration) The first day at Japanese language school. When Kai entered the classroom, the teacher smiled warmly. / Sakura-sensei: Everyone, nice to meet you. I'm Sakura, your homeroom teacher. Let's do our best together starting today. / Kai: (inner voice) I'm glad the teacher seems kind... / Sakura-sensei: Now, let's greet the person next to you. / Mina: Nice to meet you, I'm Mina. / Kai: I'm Kai. Pleased to meet you. / (Narration) Sakura-sensei's polite Japanese and Mina's smile. Kai's new daily life began right here.</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>はじめまして／〜ましょう／よろしく お願いします</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>さくら先生 デビュー＋ミナと同級。ていねい語の手本。</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>学びの場のスタート。</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:ナレーター/さくら先生/カイ/ミナ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
